--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -3983,7 +3983,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:dimension ref="A1:AC30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="58" hidden="0" customWidth="1"/>
@@ -6139,25 +6140,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/core/CPathFinder.cpp</x:v>
       </x:c>
       <x:c r="Q27" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R27" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R27" s="39" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
+      </x:c>
       <x:c r="S27" s="39"/>
-      <x:c r="T27" s="39"/>
-      <x:c r="U27" s="39"/>
-      <x:c r="V27" s="39"/>
-      <x:c r="W27" s="39"/>
+      <x:c r="T27" s="39" t="str">
+        <x:v>8f10594c-ba5d-4625-bc96-935dda260806</x:v>
+      </x:c>
+      <x:c r="U27" s="39" t="str">
+        <x:v>2026-06-30T05:31:51Z</x:v>
+      </x:c>
+      <x:c r="V27" s="39" t="str">
+        <x:v>2026-06-30T05:31:51Z</x:v>
+      </x:c>
+      <x:c r="W27" s="39" t="str">
+        <x:v>2026-07-01T05:31:51Z</x:v>
+      </x:c>
       <x:c r="X27" s="39"/>
       <x:c r="Y27" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z27" s="39" t="str">
-        <x:v>Migrated from GitHub issue #675; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
       </x:c>
       <x:c r="AA27" s="39"/>
       <x:c r="AB27" s="39"/>
       <x:c r="AC27" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="72" customHeight="1">
@@ -6425,7 +6436,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6ad6fa389ea467f"/>
+    <x:tablePart r:id="Rd6ad6fa389ea467f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6061,25 +6061,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/save format/schema helpers</x:v>
       </x:c>
       <x:c r="Q26" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R26" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R26" s="36" t="str">
+        <x:v>controller/ctrl-vm-4024-7534d796/subagent-2</x:v>
+      </x:c>
       <x:c r="S26" s="36"/>
-      <x:c r="T26" s="36"/>
-      <x:c r="U26" s="36"/>
-      <x:c r="V26" s="36"/>
-      <x:c r="W26" s="36"/>
+      <x:c r="T26" s="36" t="str">
+        <x:v>14969684-0d98-40aa-9eee-da188f53d795</x:v>
+      </x:c>
+      <x:c r="U26" s="36" t="str">
+        <x:v>2026-06-30T10:20:13Z</x:v>
+      </x:c>
+      <x:c r="V26" s="36" t="str">
+        <x:v>2026-06-30T10:20:13Z</x:v>
+      </x:c>
+      <x:c r="W26" s="36" t="str">
+        <x:v>2026-07-01T10:20:13Z</x:v>
+      </x:c>
       <x:c r="X26" s="36"/>
       <x:c r="Y26" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z26" s="36" t="str">
-        <x:v>Migrated from GitHub issue #674; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-2</x:v>
       </x:c>
       <x:c r="AA26" s="36"/>
       <x:c r="AB26" s="36"/>
       <x:c r="AC26" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5906,25 +5906,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/game_simulation.py</x:v>
       </x:c>
       <x:c r="Q24" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R24" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R24" s="36" t="str">
+        <x:v>controller/ctrl-vm-4024-7534d796/subagent-4</x:v>
+      </x:c>
       <x:c r="S24" s="36"/>
-      <x:c r="T24" s="36"/>
-      <x:c r="U24" s="36"/>
-      <x:c r="V24" s="36"/>
-      <x:c r="W24" s="36"/>
+      <x:c r="T24" s="36" t="str">
+        <x:v>3992c184-c78b-480e-9626-73e7d5c78d21</x:v>
+      </x:c>
+      <x:c r="U24" s="36" t="str">
+        <x:v>2026-06-30T10:25:40Z</x:v>
+      </x:c>
+      <x:c r="V24" s="36" t="str">
+        <x:v>2026-06-30T10:25:40Z</x:v>
+      </x:c>
+      <x:c r="W24" s="36" t="str">
+        <x:v>2026-07-01T10:25:40Z</x:v>
+      </x:c>
       <x:c r="X24" s="36"/>
       <x:c r="Y24" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z24" s="36" t="str">
-        <x:v>Migrated from GitHub issue #672; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-4</x:v>
       </x:c>
       <x:c r="AA24" s="36"/>
       <x:c r="AB24" s="36"/>
       <x:c r="AC24" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6160,30 +6160,22 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/core/CPathFinder.cpp</x:v>
       </x:c>
       <x:c r="Q27" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="R27" s="39" t="str">
-        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
-      </x:c>
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R27" s="39"/>
       <x:c r="S27" s="39"/>
-      <x:c r="T27" s="39" t="str">
-        <x:v>8f10594c-ba5d-4625-bc96-935dda260806</x:v>
-      </x:c>
-      <x:c r="U27" s="39" t="str">
-        <x:v>2026-06-30T05:31:51Z</x:v>
-      </x:c>
+      <x:c r="T27" s="39"/>
+      <x:c r="U27" s="39"/>
       <x:c r="V27" s="39" t="str">
-        <x:v>2026-06-30T05:31:51Z</x:v>
-      </x:c>
-      <x:c r="W27" s="39" t="str">
-        <x:v>2026-07-01T05:31:51Z</x:v>
-      </x:c>
+        <x:v>2026-06-30T10:47:27Z</x:v>
+      </x:c>
+      <x:c r="W27" s="39"/>
       <x:c r="X27" s="39"/>
       <x:c r="Y27" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z27" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
+        <x:v>Released by controller ctrl-vm-4026-9b5a29b5: dispatched worker was cut off by a session/usage limit before any implementation (empty working tree). No material work done; returning to NOT_STARTED for re-dispatch.</x:v>
       </x:c>
       <x:c r="AA27" s="39"/>
       <x:c r="AB27" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6160,27 +6160,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/core/CPathFinder.cpp</x:v>
       </x:c>
       <x:c r="Q27" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R27" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R27" s="39" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
+      </x:c>
       <x:c r="S27" s="39"/>
-      <x:c r="T27" s="39"/>
-      <x:c r="U27" s="39"/>
+      <x:c r="T27" s="39" t="str">
+        <x:v>3c1e98e5-1876-43a0-9d5a-3d32385cb41b</x:v>
+      </x:c>
+      <x:c r="U27" s="39" t="str">
+        <x:v>2026-06-30T10:50:10Z</x:v>
+      </x:c>
       <x:c r="V27" s="39" t="str">
-        <x:v>2026-06-30T10:47:27Z</x:v>
-      </x:c>
-      <x:c r="W27" s="39"/>
+        <x:v>2026-06-30T10:50:10Z</x:v>
+      </x:c>
+      <x:c r="W27" s="39" t="str">
+        <x:v>2026-07-01T10:50:10Z</x:v>
+      </x:c>
       <x:c r="X27" s="39"/>
       <x:c r="Y27" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z27" s="39" t="str">
-        <x:v>Released by controller ctrl-vm-4026-9b5a29b5: dispatched worker was cut off by a session/usage limit before any implementation (empty working tree). No material work done; returning to NOT_STARTED for re-dispatch.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
       </x:c>
       <x:c r="AA27" s="39"/>
       <x:c r="AB27" s="39"/>
       <x:c r="AC27" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6248,25 +6248,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/queue delivery documentation</x:v>
       </x:c>
       <x:c r="Q28" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R28" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R28" s="36" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-3</x:v>
+      </x:c>
       <x:c r="S28" s="36"/>
-      <x:c r="T28" s="36"/>
-      <x:c r="U28" s="36"/>
-      <x:c r="V28" s="36"/>
-      <x:c r="W28" s="36"/>
+      <x:c r="T28" s="36" t="str">
+        <x:v>fc03292a-02c4-44df-b1d5-5602832f0e6f</x:v>
+      </x:c>
+      <x:c r="U28" s="36" t="str">
+        <x:v>2026-06-30T10:54:14Z</x:v>
+      </x:c>
+      <x:c r="V28" s="36" t="str">
+        <x:v>2026-06-30T10:54:14Z</x:v>
+      </x:c>
+      <x:c r="W28" s="36" t="str">
+        <x:v>2026-07-01T10:54:14Z</x:v>
+      </x:c>
       <x:c r="X28" s="36"/>
       <x:c r="Y28" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z28" s="36" t="str">
-        <x:v>Migrated from GitHub issue #676; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-3</x:v>
       </x:c>
       <x:c r="AA28" s="36"/>
       <x:c r="AB28" s="36"/>
       <x:c r="AC28" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6337,25 +6337,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/config/graphics.json</x:v>
       </x:c>
       <x:c r="Q29" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R29" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R29" s="39" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-3</x:v>
+      </x:c>
       <x:c r="S29" s="39"/>
-      <x:c r="T29" s="39"/>
-      <x:c r="U29" s="39"/>
-      <x:c r="V29" s="39"/>
-      <x:c r="W29" s="39"/>
+      <x:c r="T29" s="39" t="str">
+        <x:v>e68f3200-ee72-4c8e-a967-e5fe77ddefa8</x:v>
+      </x:c>
+      <x:c r="U29" s="39" t="str">
+        <x:v>2026-06-30T10:56:52Z</x:v>
+      </x:c>
+      <x:c r="V29" s="39" t="str">
+        <x:v>2026-06-30T10:56:52Z</x:v>
+      </x:c>
+      <x:c r="W29" s="39" t="str">
+        <x:v>2026-07-01T10:56:52Z</x:v>
+      </x:c>
       <x:c r="X29" s="39"/>
       <x:c r="Y29" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z29" s="39" t="str">
-        <x:v>Migrated from GitHub issue #677; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-3</x:v>
       </x:c>
       <x:c r="AA29" s="39"/>
       <x:c r="AB29" s="39"/>
       <x:c r="AC29" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6248,7 +6248,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/queue delivery documentation</x:v>
       </x:c>
       <x:c r="Q28" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R28" s="36" t="str">
         <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-3</x:v>
@@ -6261,20 +6261,24 @@
         <x:v>2026-06-30T10:54:14Z</x:v>
       </x:c>
       <x:c r="V28" s="36" t="str">
-        <x:v>2026-06-30T10:54:14Z</x:v>
-      </x:c>
-      <x:c r="W28" s="36" t="str">
-        <x:v>2026-07-01T10:54:14Z</x:v>
-      </x:c>
-      <x:c r="X28" s="36"/>
+        <x:v>2026-06-30T11:02:32Z</x:v>
+      </x:c>
+      <x:c r="W28" s="36"/>
+      <x:c r="X28" s="36" t="str">
+        <x:v>2026-06-30T11:02:32Z</x:v>
+      </x:c>
       <x:c r="Y28" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z28" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-3</x:v>
-      </x:c>
-      <x:c r="AA28" s="36"/>
-      <x:c r="AB28" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA28" s="36" t="str">
+        <x:v>Replaced the opt-out implementation-PR auto-merge default with a four-state authorization gate (allowed/user-authorized/disallowed/unknown) across AGENTS.md, the controller prompt, and the agent-queue doc; unknown/disallowed leaves the PR open and reports a blocker. Preserved the bounded workbook-only queue-state immediate-merge exception. Integrated with the existing controller_resource_audit.py merge-policy/branch-protection probing.</x:v>
+      </x:c>
+      <x:c r="AB28" s="36" t="str">
+        <x:v>python3 -m unittest tests.test_prompt_inventory -v: 6 passed (incl. new regression). GitHub Actions build workflow on PR #916: linux SUCCESS, linux-fast SUCCESS, validate SUCCESS, export SUCCESS; windows/windows-deps/linux-coverage skipped (workflow-only classification). Merged to main as c498086.</x:v>
+      </x:c>
       <x:c r="AC28" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5671,25 +5671,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/AGENTS.md</x:v>
       </x:c>
       <x:c r="Q21" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R21" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R21" s="39" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-5</x:v>
+      </x:c>
       <x:c r="S21" s="39"/>
-      <x:c r="T21" s="39"/>
-      <x:c r="U21" s="39"/>
-      <x:c r="V21" s="39"/>
-      <x:c r="W21" s="39"/>
+      <x:c r="T21" s="39" t="str">
+        <x:v>4d74f425-a323-41d6-931b-13cf0d913a14</x:v>
+      </x:c>
+      <x:c r="U21" s="39" t="str">
+        <x:v>2026-06-30T11:06:18Z</x:v>
+      </x:c>
+      <x:c r="V21" s="39" t="str">
+        <x:v>2026-06-30T11:06:18Z</x:v>
+      </x:c>
+      <x:c r="W21" s="39" t="str">
+        <x:v>2026-07-01T11:06:18Z</x:v>
+      </x:c>
       <x:c r="X21" s="39"/>
       <x:c r="Y21" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z21" s="39" t="str">
-        <x:v>Migrated from GitHub issue #669; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-5</x:v>
       </x:c>
       <x:c r="AA21" s="39"/>
       <x:c r="AB21" s="39"/>
       <x:c r="AC21" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5929,17 +5929,17 @@
         <x:v>2026-06-30T10:25:40Z</x:v>
       </x:c>
       <x:c r="V24" s="36" t="str">
-        <x:v>2026-06-30T10:25:40Z</x:v>
+        <x:v>2026-06-30T11:42:03Z</x:v>
       </x:c>
       <x:c r="W24" s="36" t="str">
-        <x:v>2026-07-01T10:25:40Z</x:v>
+        <x:v>2026-07-01T11:42:03Z</x:v>
       </x:c>
       <x:c r="X24" s="36"/>
       <x:c r="Y24" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Z24" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-4</x:v>
+        <x:v>Implementation complete and pushed (PR #898 / #899); blocked on broken main build CI (scene-manager regression test_scene_manager_transition_requested_during_combat_preserves_source_map, user-owned fix). Awaiting CI restoration to merge.</x:v>
       </x:c>
       <x:c r="AA24" s="36"/>
       <x:c r="AB24" s="36"/>
@@ -6094,17 +6094,17 @@
         <x:v>2026-06-30T10:20:13Z</x:v>
       </x:c>
       <x:c r="V26" s="36" t="str">
-        <x:v>2026-06-30T10:20:13Z</x:v>
+        <x:v>2026-06-30T11:42:03Z</x:v>
       </x:c>
       <x:c r="W26" s="36" t="str">
-        <x:v>2026-07-01T10:20:13Z</x:v>
+        <x:v>2026-07-01T11:42:03Z</x:v>
       </x:c>
       <x:c r="X26" s="36"/>
       <x:c r="Y26" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Z26" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-2</x:v>
+        <x:v>Implementation complete and pushed (PR #898 / #899); blocked on broken main build CI (scene-manager regression test_scene_manager_transition_requested_during_combat_preserves_source_map, user-owned fix). Awaiting CI restoration to merge.</x:v>
       </x:c>
       <x:c r="AA26" s="36"/>
       <x:c r="AB26" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6364,17 +6364,17 @@
         <x:v>2026-06-30T10:56:52Z</x:v>
       </x:c>
       <x:c r="V29" s="39" t="str">
-        <x:v>2026-06-30T10:56:52Z</x:v>
+        <x:v>2026-06-30T12:06:49Z</x:v>
       </x:c>
       <x:c r="W29" s="39" t="str">
-        <x:v>2026-07-01T10:56:52Z</x:v>
+        <x:v>2026-07-01T12:06:49Z</x:v>
       </x:c>
       <x:c r="X29" s="39"/>
       <x:c r="Y29" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z29" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-3</x:v>
+        <x:v>Implementation complete and PR open (#926); awaiting main-build unblock via PR #945 (scene-manager source-map leak fix).</x:v>
       </x:c>
       <x:c r="AA29" s="39"/>
       <x:c r="AB29" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5684,17 +5684,17 @@
         <x:v>2026-06-30T11:06:18Z</x:v>
       </x:c>
       <x:c r="V21" s="39" t="str">
-        <x:v>2026-06-30T11:06:18Z</x:v>
+        <x:v>2026-06-30T12:22:37Z</x:v>
       </x:c>
       <x:c r="W21" s="39" t="str">
-        <x:v>2026-07-01T11:06:18Z</x:v>
+        <x:v>2026-07-01T12:22:37Z</x:v>
       </x:c>
       <x:c r="X21" s="39"/>
       <x:c r="Y21" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z21" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-5</x:v>
+        <x:v>Implementation complete and pushed; blocked only on main-red native CI (test_scene_manager_transition_requested_during_combat_preserves_source_map, a pre-existing combat-transition regression on main, observed 05b033bd). Do not reclaim. awaiting user review of authority-machinery PR #934.</x:v>
       </x:c>
       <x:c r="AA21" s="39"/>
       <x:c r="AB21" s="39"/>
@@ -6183,17 +6183,17 @@
         <x:v>2026-06-30T10:50:10Z</x:v>
       </x:c>
       <x:c r="V27" s="39" t="str">
-        <x:v>2026-06-30T10:50:10Z</x:v>
+        <x:v>2026-06-30T12:22:37Z</x:v>
       </x:c>
       <x:c r="W27" s="39" t="str">
-        <x:v>2026-07-01T10:50:10Z</x:v>
+        <x:v>2026-07-01T12:22:37Z</x:v>
       </x:c>
       <x:c r="X27" s="39"/>
       <x:c r="Y27" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z27" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
+        <x:v>Implementation complete and pushed; blocked only on main-red native CI (test_scene_manager_transition_requested_during_combat_preserves_source_map, a pre-existing combat-transition regression on main, observed 05b033bd). Do not reclaim.</x:v>
       </x:c>
       <x:c r="AA27" s="39"/>
       <x:c r="AB27" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6170,7 +6170,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/core/CPathFinder.cpp</x:v>
       </x:c>
       <x:c r="Q27" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R27" s="39" t="str">
         <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-1</x:v>
@@ -6183,20 +6183,24 @@
         <x:v>2026-06-30T10:50:10Z</x:v>
       </x:c>
       <x:c r="V27" s="39" t="str">
-        <x:v>2026-06-30T12:22:37Z</x:v>
-      </x:c>
-      <x:c r="W27" s="39" t="str">
-        <x:v>2026-07-01T12:22:37Z</x:v>
-      </x:c>
-      <x:c r="X27" s="39"/>
+        <x:v>2026-06-30T12:50:27Z</x:v>
+      </x:c>
+      <x:c r="W27" s="39"/>
+      <x:c r="X27" s="39" t="str">
+        <x:v>2026-06-30T12:50:27Z</x:v>
+      </x:c>
       <x:c r="Y27" s="39" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z27" s="39" t="str">
-        <x:v>Implementation complete and pushed; blocked only on main-red native CI (test_scene_manager_transition_requested_during_combat_preserves_source_map, a pre-existing combat-transition regression on main, observed 05b033bd). Do not reclaim.</x:v>
-      </x:c>
-      <x:c r="AA27" s="39"/>
-      <x:c r="AB27" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA27" s="39" t="str">
+        <x:v>Restricted MCP pathfinding resource consumption: mcp.py validates setTarget args (rejects extreme-magnitude/out-of-bounds/non-passable targets); CController::setTarget rejects out-of-map-extent targets before pathfinding; CMap gained public isWithinBounds; CPathFinder added a goal-relative coordinate-envelope budget (4*manhattan+512, sized so wrapping maps are not over-pruned) and a max path-length guard alongside the existing 1M-node cap. MCP runtime tests + native pathfinder envelope tests added.</x:v>
+      </x:c>
+      <x:c r="AB27" s="39" t="str">
+        <x:v>GitHub Actions on PR #923 (final run on unblocked main): linux SUCCESS, windows SUCCESS, windows-deps/linux-fast/validate SUCCESS. Native pathfinder tests + full Python suite (incl. MCP guard tests and the previously-regressed change-map test) passed. Merged to main as 8fa0ef96.</x:v>
+      </x:c>
       <x:c r="AC27" s="39" t="n">
         <x:v>2</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6442,25 +6442,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/game.py</x:v>
       </x:c>
       <x:c r="Q30" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R30" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R30" s="36" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-10</x:v>
+      </x:c>
       <x:c r="S30" s="36"/>
-      <x:c r="T30" s="36"/>
-      <x:c r="U30" s="36"/>
-      <x:c r="V30" s="36"/>
-      <x:c r="W30" s="36"/>
+      <x:c r="T30" s="36" t="str">
+        <x:v>78738aaf-943f-42cc-b6d3-5620e1fbf8c4</x:v>
+      </x:c>
+      <x:c r="U30" s="36" t="str">
+        <x:v>2026-06-30T13:04:28Z</x:v>
+      </x:c>
+      <x:c r="V30" s="36" t="str">
+        <x:v>2026-06-30T13:04:28Z</x:v>
+      </x:c>
+      <x:c r="W30" s="36" t="str">
+        <x:v>2026-07-01T13:04:28Z</x:v>
+      </x:c>
       <x:c r="X30" s="36"/>
       <x:c r="Y30" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z30" s="36" t="str">
-        <x:v>Migrated from GitHub issue #678; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-10</x:v>
       </x:c>
       <x:c r="AA30" s="36"/>
       <x:c r="AB30" s="36"/>
       <x:c r="AC30" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6368,17 +6368,17 @@
         <x:v>2026-06-30T10:56:52Z</x:v>
       </x:c>
       <x:c r="V29" s="39" t="str">
-        <x:v>2026-06-30T12:06:49Z</x:v>
+        <x:v>2026-06-30T13:14:23Z</x:v>
       </x:c>
       <x:c r="W29" s="39" t="str">
-        <x:v>2026-07-01T12:06:49Z</x:v>
+        <x:v>2026-07-01T13:14:23Z</x:v>
       </x:c>
       <x:c r="X29" s="39"/>
       <x:c r="Y29" s="39" t="n">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="Z29" s="39" t="str">
-        <x:v>Implementation complete and PR open (#926); awaiting main-build unblock via PR #945 (scene-manager source-map leak fix).</x:v>
+        <x:v>Impl complete; rebased PR #926 re-running on green main (unblocked by #945). Prior CI run stalled in congested queue; re-triggered.</x:v>
       </x:c>
       <x:c r="AA29" s="39"/>
       <x:c r="AB29" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6355,7 +6355,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/config/graphics.json</x:v>
       </x:c>
       <x:c r="Q29" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R29" s="39" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-3</x:v>
@@ -6368,20 +6368,24 @@
         <x:v>2026-06-30T10:56:52Z</x:v>
       </x:c>
       <x:c r="V29" s="39" t="str">
-        <x:v>2026-06-30T13:14:23Z</x:v>
-      </x:c>
-      <x:c r="W29" s="39" t="str">
-        <x:v>2026-07-01T13:14:23Z</x:v>
-      </x:c>
-      <x:c r="X29" s="39"/>
+        <x:v>2026-06-30T14:00:48Z</x:v>
+      </x:c>
+      <x:c r="W29" s="39"/>
+      <x:c r="X29" s="39" t="str">
+        <x:v>2026-06-30T14:00:48Z</x:v>
+      </x:c>
       <x:c r="Y29" s="39" t="n">
-        <x:v>92</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z29" s="39" t="str">
-        <x:v>Impl complete; rebased PR #926 re-running on green main (unblocked by #945). Prior CI run stalled in congested queue; re-triggered.</x:v>
-      </x:c>
-      <x:c r="AA29" s="39"/>
-      <x:c r="AB29" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA29" s="39" t="str">
+        <x:v>Bounded minimap rendering against malformed/extreme map extents. Clamped attacker-authorable xBound/yBound level metadata in CLoader; added MAX_MINIMAP_LEVEL_EXTENT with overflow-safe (long long) bounds checks in CMinimapGraphicsObject (get_level_bounds fails closed to a bounded placeholder; make_scale overflow-safe). Added 5 GUI regression tests (extreme/overflow/sparse/negative-origin/normal). No save/map format change; legitimate maps render unchanged.</x:v>
+      </x:c>
+      <x:c r="AB29" s="39" t="str">
+        <x:v>CI: GitHub Actions build run #2101 (head 75ee6700) on green main -&gt; all 5 jobs success (linux-fast, windows-deps, linux, windows, linux-coverage incl. test (c++)+test (python gameplay)+coverage). Implementation PR #926 merged to main (squash 366edbce). clang-format + git diff --check clean.</x:v>
+      </x:c>
       <x:c r="AC29" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6446,7 +6446,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/game.py</x:v>
       </x:c>
       <x:c r="Q30" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R30" s="36" t="str">
         <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-10</x:v>
@@ -6459,20 +6459,24 @@
         <x:v>2026-06-30T13:04:28Z</x:v>
       </x:c>
       <x:c r="V30" s="36" t="str">
-        <x:v>2026-06-30T13:04:28Z</x:v>
-      </x:c>
-      <x:c r="W30" s="36" t="str">
-        <x:v>2026-07-01T13:04:28Z</x:v>
-      </x:c>
-      <x:c r="X30" s="36"/>
+        <x:v>2026-06-30T14:01:45Z</x:v>
+      </x:c>
+      <x:c r="W30" s="36"/>
+      <x:c r="X30" s="36" t="str">
+        <x:v>2026-06-30T14:01:45Z</x:v>
+      </x:c>
       <x:c r="Y30" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z30" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-10</x:v>
-      </x:c>
-      <x:c r="AA30" s="36"/>
-      <x:c r="AB30" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA30" s="36" t="str">
+        <x:v>Made config-driven reflective callbacks fail closed, mirroring res/game.py's public-callback contract. Audited all reflective dispatch points; the two unguarded ones (CGameCharacterPanel char-sheet accessor, CGameObject signal-&gt;slot dispatch) now empty-guard + try/catch + log (actions no-op, conditions return false), so a bad/throwing callback cannot crash the render or event loop. Extended validate_content.py to flag empty/non-identifier/private/dunder/invokeAction/invokeCondition dialog method names. Native gui+signal-slot regressions and 5 validator tests added.</x:v>
+      </x:c>
+      <x:c r="AB30" s="36" t="str">
+        <x:v>GitHub Actions on PR #974 (green main): linux SUCCESS, windows SUCCESS, windows-deps/linux-fast/validate SUCCESS. tests.test_content_validator 49 passed; native gui_unit_tests/object_unit_tests + full suite passed. Merged to main as c433d1c9.</x:v>
+      </x:c>
       <x:c r="AC30" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5839,25 +5839,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/object/CGameObject.cpp</x:v>
       </x:c>
       <x:c r="Q23" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R23" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R23" s="39" t="str">
+        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-11</x:v>
+      </x:c>
       <x:c r="S23" s="39"/>
-      <x:c r="T23" s="39"/>
-      <x:c r="U23" s="39"/>
-      <x:c r="V23" s="39"/>
-      <x:c r="W23" s="39"/>
+      <x:c r="T23" s="39" t="str">
+        <x:v>2829d4f9-adf5-4bcf-9a66-839425db0dc8</x:v>
+      </x:c>
+      <x:c r="U23" s="39" t="str">
+        <x:v>2026-06-30T14:03:01Z</x:v>
+      </x:c>
+      <x:c r="V23" s="39" t="str">
+        <x:v>2026-06-30T14:03:01Z</x:v>
+      </x:c>
+      <x:c r="W23" s="39" t="str">
+        <x:v>2026-07-01T14:03:01Z</x:v>
+      </x:c>
       <x:c r="X23" s="39"/>
       <x:c r="Y23" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z23" s="39" t="str">
-        <x:v>Migrated from GitHub issue #671; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-11</x:v>
       </x:c>
       <x:c r="AA23" s="39"/>
       <x:c r="AB23" s="39"/>
       <x:c r="AC23" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5839,7 +5839,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/object/CGameObject.cpp</x:v>
       </x:c>
       <x:c r="Q23" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R23" s="39" t="str">
         <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-11</x:v>
@@ -5852,20 +5852,24 @@
         <x:v>2026-06-30T14:03:01Z</x:v>
       </x:c>
       <x:c r="V23" s="39" t="str">
-        <x:v>2026-06-30T14:03:01Z</x:v>
-      </x:c>
-      <x:c r="W23" s="39" t="str">
-        <x:v>2026-07-01T14:03:01Z</x:v>
-      </x:c>
-      <x:c r="X23" s="39"/>
+        <x:v>2026-06-30T14:42:22Z</x:v>
+      </x:c>
+      <x:c r="W23" s="39"/>
+      <x:c r="X23" s="39" t="str">
+        <x:v>2026-06-30T14:42:22Z</x:v>
+      </x:c>
       <x:c r="Y23" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z23" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4026-9b5a29b5/subagent-11</x:v>
-      </x:c>
-      <x:c r="AA23" s="39"/>
-      <x:c r="AB23" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA23" s="39" t="str">
+        <x:v>Merged PR #987 (923f1f52): dynamic property notifications can no longer spoof typed engine signals. Added CGameObject::isReservedTypedSignalName registry; notifyPropertyChangedWithoutInvalidation drops+logs per-property &lt;name&gt;Changed emissions that collide with reserved typed names; CListView skips+logs colliding refreshProperties names. Native linux+windows green.</x:v>
+      </x:c>
+      <x:c r="AB23" s="39" t="str">
+        <x:v>linux+windows native CI green on PR #987; test_object.cpp + test_gui.cpp regressions: dynamic property cannot spoof typed signal, typed signal still fires, refreshProperty collision fails closed while valid property refreshes.</x:v>
+      </x:c>
       <x:c r="AC23" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6095,7 +6095,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/save format/schema helpers</x:v>
       </x:c>
       <x:c r="Q26" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R26" s="36" t="str">
         <x:v>controller/ctrl-vm-4024-7534d796/subagent-2</x:v>
@@ -6108,20 +6108,24 @@
         <x:v>2026-06-30T10:20:13Z</x:v>
       </x:c>
       <x:c r="V26" s="36" t="str">
-        <x:v>2026-06-30T11:42:03Z</x:v>
-      </x:c>
-      <x:c r="W26" s="36" t="str">
-        <x:v>2026-07-01T11:42:03Z</x:v>
-      </x:c>
-      <x:c r="X26" s="36"/>
+        <x:v>2026-06-30T19:58:43Z</x:v>
+      </x:c>
+      <x:c r="W26" s="36"/>
+      <x:c r="X26" s="36" t="str">
+        <x:v>2026-06-30T19:58:43Z</x:v>
+      </x:c>
       <x:c r="Y26" s="36" t="n">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z26" s="36" t="str">
-        <x:v>Implementation complete and pushed (PR #898 / #899); blocked on broken main build CI (scene-manager regression test_scene_manager_transition_requested_during_combat_preserves_source_map, user-owned fix). Awaiting CI restoration to merge.</x:v>
-      </x:c>
-      <x:c r="AA26" s="36"/>
-      <x:c r="AB26" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA26" s="36" t="str">
+        <x:v>Bounded saved-quest reference traversal during load to prevent stack exhaustion / CPU DoS from crafted save JSON. Added iterative, bounded structure validation in CSaveFormat (MAX_DOCUMENT_DEPTH=200, MAX_DOCUMENT_NODES=8M, MAX_CONTAINER_ENTRIES=1M) invoked at the top of decodeDocument, and rewrote collect_saved_quest_refs in CLoader as an iterative work-stack with a node ceiling. Reuses the existing std::expected loader-error path; rejects oversized/over-deep saves with a clear reason while loading legitimate saves unchanged (real fixtures max depth 9). Added native (test_core.cpp) and Python (test.py) regressions for boundary, oversize, repeated-ref, and normal round-trip cases. The detachPlayer API is unrelated/untouched.</x:v>
+      </x:c>
+      <x:c r="AB26" s="36" t="str">
+        <x:v>CI (PR #898 on green main) check runs: linux=success, windows=success, windows-deps=success, linux-coverage=success, linux-fast=success, validate=success, export=success. Full native build + ctest + python suite + coverage all passed. Implementation PR #898 merged to main as 2646b8946c7fbd5c95619df0f29fa3543ef4d1fc.</x:v>
+      </x:c>
       <x:c r="AC26" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5930,7 +5930,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/game_simulation.py</x:v>
       </x:c>
       <x:c r="Q24" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R24" s="36" t="str">
         <x:v>controller/ctrl-vm-4024-7534d796/subagent-4</x:v>
@@ -5943,20 +5943,24 @@
         <x:v>2026-06-30T10:25:40Z</x:v>
       </x:c>
       <x:c r="V24" s="36" t="str">
-        <x:v>2026-06-30T11:42:03Z</x:v>
-      </x:c>
-      <x:c r="W24" s="36" t="str">
-        <x:v>2026-07-01T11:42:03Z</x:v>
-      </x:c>
-      <x:c r="X24" s="36"/>
+        <x:v>2026-06-30T19:59:34Z</x:v>
+      </x:c>
+      <x:c r="W24" s="36"/>
+      <x:c r="X24" s="36" t="str">
+        <x:v>2026-06-30T19:59:34Z</x:v>
+      </x:c>
       <x:c r="Y24" s="36" t="n">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z24" s="36" t="str">
-        <x:v>Implementation complete and pushed (PR #898 / #899); blocked on broken main build CI (scene-manager regression test_scene_manager_transition_requested_during_combat_preserves_source_map, user-owned fix). Awaiting CI restoration to merge.</x:v>
-      </x:c>
-      <x:c r="AA24" s="36"/>
-      <x:c r="AB24" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA24" s="36" t="str">
+        <x:v>Enforced per-action iteration limits in MCP simulation_run to prevent a single step (extreme turns/times/max_iterations/max_turns) from bypassing the step cap and causing CPU-heavy loops. Added a shared per-action limits block plus validateSteps() and a cumulative iteration budget in game_simulation.py, validating all attacker-controlled counts before any loop runs and rejecting non-integer/negative/above-limit values with a structured SimulationError identifying the offending action index and field. Wired validateSteps into runSteps/runSimulation and gated mcp._simulation_run on it so over-budget payloads do no engine work; repeated/nested actions add to one running budget and cannot multiply it. Added 22 engine-free, timeout-free regressions (spy event loop proves rejected actions run zero iterations). Backward-compatible: defaults unchanged.</x:v>
+      </x:c>
+      <x:c r="AB24" s="36" t="str">
+        <x:v>CI (PR #899 on green main) check runs: linux=success, windows=success, windows-deps=success, linux-fast=success, validate=success, export=success; linux-coverage=skipped (no coverage-trigger paths). Implementation PR #899 merged to main as b122be562dc4636bdb5403f34aa988ab91407e2b. Worker-run focused tests: tests.security.test_simulation_action_limits 22 passed; tests.security.test_mcp_hardening 4 passed.</x:v>
+      </x:c>
       <x:c r="AC24" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5760,25 +5760,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/game.py</x:v>
       </x:c>
       <x:c r="Q22" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R22" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R22" s="36" t="str">
+        <x:v>controller/ctrl-vm-4024-7534d796/subagent-10</x:v>
+      </x:c>
       <x:c r="S22" s="36"/>
-      <x:c r="T22" s="36"/>
-      <x:c r="U22" s="36"/>
-      <x:c r="V22" s="36"/>
-      <x:c r="W22" s="36"/>
+      <x:c r="T22" s="36" t="str">
+        <x:v>866b9190-9672-423a-84e6-7a89992a38e3</x:v>
+      </x:c>
+      <x:c r="U22" s="36" t="str">
+        <x:v>2026-06-30T20:07:26Z</x:v>
+      </x:c>
+      <x:c r="V22" s="36" t="str">
+        <x:v>2026-06-30T20:07:26Z</x:v>
+      </x:c>
+      <x:c r="W22" s="36" t="str">
+        <x:v>2026-07-01T20:07:26Z</x:v>
+      </x:c>
       <x:c r="X22" s="36"/>
       <x:c r="Y22" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z22" s="36" t="str">
-        <x:v>Migrated from GitHub issue #670; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-10</x:v>
       </x:c>
       <x:c r="AA22" s="36"/>
       <x:c r="AB22" s="36"/>
       <x:c r="AC22" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6032,25 +6032,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/vcpkg triplets/manifests</x:v>
       </x:c>
       <x:c r="Q25" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R25" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R25" s="39" t="str">
+        <x:v>controller/ctrl-vm-4024-7534d796/subagent-11</x:v>
+      </x:c>
       <x:c r="S25" s="39"/>
-      <x:c r="T25" s="39"/>
-      <x:c r="U25" s="39"/>
-      <x:c r="V25" s="39"/>
-      <x:c r="W25" s="39"/>
+      <x:c r="T25" s="39" t="str">
+        <x:v>ff73ecb2-7600-431d-92ba-da44273f9606</x:v>
+      </x:c>
+      <x:c r="U25" s="39" t="str">
+        <x:v>2026-06-30T20:15:07Z</x:v>
+      </x:c>
+      <x:c r="V25" s="39" t="str">
+        <x:v>2026-06-30T20:15:07Z</x:v>
+      </x:c>
+      <x:c r="W25" s="39" t="str">
+        <x:v>2026-07-01T20:15:07Z</x:v>
+      </x:c>
       <x:c r="X25" s="39"/>
       <x:c r="Y25" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z25" s="39" t="str">
-        <x:v>Migrated from GitHub issue #673; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-11</x:v>
       </x:c>
       <x:c r="AA25" s="39"/>
       <x:c r="AB25" s="39"/>
       <x:c r="AC25" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5038,25 +5038,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.cpp</x:v>
       </x:c>
       <x:c r="Q13" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R13" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R13" s="39" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-26</x:v>
+      </x:c>
       <x:c r="S13" s="39"/>
-      <x:c r="T13" s="39"/>
-      <x:c r="U13" s="39"/>
-      <x:c r="V13" s="39"/>
-      <x:c r="W13" s="39"/>
+      <x:c r="T13" s="39" t="str">
+        <x:v>c0935304-fd88-4899-8303-41fad1683ec5</x:v>
+      </x:c>
+      <x:c r="U13" s="39" t="str">
+        <x:v>2026-06-30T23:22:21Z</x:v>
+      </x:c>
+      <x:c r="V13" s="39" t="str">
+        <x:v>2026-06-30T23:22:21Z</x:v>
+      </x:c>
+      <x:c r="W13" s="39" t="str">
+        <x:v>2026-07-01T01:22:21Z</x:v>
+      </x:c>
       <x:c r="X13" s="39"/>
       <x:c r="Y13" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z13" s="39" t="str">
-        <x:v>Migrated from GitHub issue #625; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-26</x:v>
       </x:c>
       <x:c r="AA13" s="39"/>
       <x:c r="AB13" s="39"/>
       <x:c r="AC13" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="72" customHeight="1">
@@ -5354,25 +5364,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/object/CGameGraphicsObject.cpp</x:v>
       </x:c>
       <x:c r="Q17" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R17" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R17" s="39" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-25</x:v>
+      </x:c>
       <x:c r="S17" s="39"/>
-      <x:c r="T17" s="39"/>
-      <x:c r="U17" s="39"/>
-      <x:c r="V17" s="39"/>
-      <x:c r="W17" s="39"/>
+      <x:c r="T17" s="39" t="str">
+        <x:v>be8ec7b7-1bad-4837-aa77-556fcfb20b85</x:v>
+      </x:c>
+      <x:c r="U17" s="39" t="str">
+        <x:v>2026-06-30T23:22:21Z</x:v>
+      </x:c>
+      <x:c r="V17" s="39" t="str">
+        <x:v>2026-06-30T23:22:21Z</x:v>
+      </x:c>
+      <x:c r="W17" s="39" t="str">
+        <x:v>2026-07-01T01:22:21Z</x:v>
+      </x:c>
       <x:c r="X17" s="39"/>
       <x:c r="Y17" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z17" s="39" t="str">
-        <x:v>Migrated from GitHub issue #629; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-25</x:v>
       </x:c>
       <x:c r="AA17" s="39"/>
       <x:c r="AB17" s="39"/>
       <x:c r="AC17" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5613,25 +5613,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/dialog5.json</x:v>
       </x:c>
       <x:c r="Q20" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R20" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R20" s="36" t="str">
+        <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c1</x:v>
+      </x:c>
       <x:c r="S20" s="36"/>
-      <x:c r="T20" s="36"/>
-      <x:c r="U20" s="36"/>
-      <x:c r="V20" s="36"/>
-      <x:c r="W20" s="36"/>
+      <x:c r="T20" s="36" t="str">
+        <x:v>450ea3ef-6009-4c66-a5df-03d30ae1c498</x:v>
+      </x:c>
+      <x:c r="U20" s="36" t="str">
+        <x:v>2026-06-30T23:50:55Z</x:v>
+      </x:c>
+      <x:c r="V20" s="36" t="str">
+        <x:v>2026-06-30T23:50:55Z</x:v>
+      </x:c>
+      <x:c r="W20" s="36" t="str">
+        <x:v>2026-07-01T23:50:55Z</x:v>
+      </x:c>
       <x:c r="X20" s="36"/>
       <x:c r="Y20" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z20" s="36" t="str">
-        <x:v>Migrated from GitHub issue #632; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c1</x:v>
       </x:c>
       <x:c r="AA20" s="36"/>
       <x:c r="AB20" s="36"/>
       <x:c r="AC20" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5038,7 +5038,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.cpp</x:v>
       </x:c>
       <x:c r="Q13" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R13" s="39" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-26</x:v>
@@ -5051,20 +5051,24 @@
         <x:v>2026-06-30T23:22:21Z</x:v>
       </x:c>
       <x:c r="V13" s="39" t="str">
-        <x:v>2026-06-30T23:22:21Z</x:v>
-      </x:c>
-      <x:c r="W13" s="39" t="str">
-        <x:v>2026-07-01T01:22:21Z</x:v>
-      </x:c>
-      <x:c r="X13" s="39"/>
+        <x:v>2026-07-01T00:00:31Z</x:v>
+      </x:c>
+      <x:c r="W13" s="39"/>
+      <x:c r="X13" s="39" t="str">
+        <x:v>2026-07-01T00:00:31Z</x:v>
+      </x:c>
       <x:c r="Y13" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z13" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-26</x:v>
-      </x:c>
-      <x:c r="AA13" s="39"/>
-      <x:c r="AB13" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA13" s="39" t="str">
+        <x:v>Added CListView dragEnabled property (default true, backward-compatible; audited all 10 CListView usages in panels.json) and gated both drag-initiation paths so a non-draggable list never calls startDragSession/capturePointer/proxy at mouse-down; left/right click + click callback still fire. panels.json sets dragEnabled false on the two interaction/command lists only. Native gui tests cover click-only press/motion/release, repeated first-select/second-confirm, inventory-still-drags regression, and panel-removal-no-dangling. Merged as PR #1131.</x:v>
+      </x:c>
+      <x:c r="AB13" s="39" t="str">
+        <x:v>ctest gui_unit_tests + gui_drag_proxy_unit_tests green on linux and windows on PR #1131; validate_content passed. All required lanes green.</x:v>
+      </x:c>
       <x:c r="AC13" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -5286,25 +5290,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/panel/CGameFightPanel.cpp</x:v>
       </x:c>
       <x:c r="Q16" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R16" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R16" s="36" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-27</x:v>
+      </x:c>
       <x:c r="S16" s="36"/>
-      <x:c r="T16" s="36"/>
-      <x:c r="U16" s="36"/>
-      <x:c r="V16" s="36"/>
-      <x:c r="W16" s="36"/>
+      <x:c r="T16" s="36" t="str">
+        <x:v>ef3a15f3-b518-47c9-967e-5ce31dd710a0</x:v>
+      </x:c>
+      <x:c r="U16" s="36" t="str">
+        <x:v>2026-07-01T00:01:55Z</x:v>
+      </x:c>
+      <x:c r="V16" s="36" t="str">
+        <x:v>2026-07-01T00:01:55Z</x:v>
+      </x:c>
+      <x:c r="W16" s="36" t="str">
+        <x:v>2026-07-01T02:01:55Z</x:v>
+      </x:c>
       <x:c r="X16" s="36"/>
       <x:c r="Y16" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z16" s="36" t="str">
-        <x:v>Migrated from GitHub issue #628; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-27</x:v>
       </x:c>
       <x:c r="AA16" s="36"/>
       <x:c r="AB16" s="36"/>
       <x:c r="AC16" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="72" customHeight="1">
@@ -5364,7 +5378,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/object/CGameGraphicsObject.cpp</x:v>
       </x:c>
       <x:c r="Q17" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R17" s="39" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-25</x:v>
@@ -5377,20 +5391,24 @@
         <x:v>2026-06-30T23:22:21Z</x:v>
       </x:c>
       <x:c r="V17" s="39" t="str">
-        <x:v>2026-06-30T23:22:21Z</x:v>
-      </x:c>
-      <x:c r="W17" s="39" t="str">
-        <x:v>2026-07-01T01:22:21Z</x:v>
-      </x:c>
-      <x:c r="X17" s="39"/>
+        <x:v>2026-07-01T00:00:31Z</x:v>
+      </x:c>
+      <x:c r="W17" s="39"/>
+      <x:c r="X17" s="39" t="str">
+        <x:v>2026-07-01T00:00:31Z</x:v>
+      </x:c>
       <x:c r="Y17" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z17" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-25</x:v>
-      </x:c>
-      <x:c r="AA17" s="39"/>
-      <x:c r="AB17" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA17" s="39" t="str">
+        <x:v>CMinimapGraphicsObject::mouseEvent now returns handled and a mouseMotionEvent override returns handled, so in-bounds pointer button/motion events are consumed and never fall through to the underlying map; wheel deliberately falls through (map zoom). Relies on the base CGameGraphicsObject dispatcher in-bounds+visibility gating. Native gui_unit_tests test_minimap_consumes_inside_pointer_events_and_preserves_outside_and_wheel covers inside-consume, outside-by-one-pixel fallthrough, wheel fallthrough, hidden-minimap, modal precedence. CGui.cpp untouched. Merged as PR #1127.</x:v>
+      </x:c>
+      <x:c r="AB17" s="39" t="str">
+        <x:v>ctest gui_unit_tests green on linux and windows on PR #1127. All required lanes green.</x:v>
+      </x:c>
       <x:c r="AC17" s="39" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -5453,25 +5471,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/dialog2.json</x:v>
       </x:c>
       <x:c r="Q18" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R18" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R18" s="36" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-28</x:v>
+      </x:c>
       <x:c r="S18" s="36"/>
-      <x:c r="T18" s="36"/>
-      <x:c r="U18" s="36"/>
-      <x:c r="V18" s="36"/>
-      <x:c r="W18" s="36"/>
+      <x:c r="T18" s="36" t="str">
+        <x:v>783ec46c-a4d5-408d-b4a7-992596f12d01</x:v>
+      </x:c>
+      <x:c r="U18" s="36" t="str">
+        <x:v>2026-07-01T00:01:55Z</x:v>
+      </x:c>
+      <x:c r="V18" s="36" t="str">
+        <x:v>2026-07-01T00:01:55Z</x:v>
+      </x:c>
+      <x:c r="W18" s="36" t="str">
+        <x:v>2026-07-01T02:01:55Z</x:v>
+      </x:c>
       <x:c r="X18" s="36"/>
       <x:c r="Y18" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z18" s="36" t="str">
-        <x:v>Migrated from GitHub issue #630; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-28</x:v>
       </x:c>
       <x:c r="AA18" s="36"/>
       <x:c r="AB18" s="36"/>
       <x:c r="AC18" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5133,25 +5133,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.h</x:v>
       </x:c>
       <x:c r="Q14" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R14" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R14" s="36" t="str">
+        <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c3</x:v>
+      </x:c>
       <x:c r="S14" s="36"/>
-      <x:c r="T14" s="36"/>
-      <x:c r="U14" s="36"/>
-      <x:c r="V14" s="36"/>
-      <x:c r="W14" s="36"/>
+      <x:c r="T14" s="36" t="str">
+        <x:v>e466d23e-436f-4898-99b2-29e799f7b94c</x:v>
+      </x:c>
+      <x:c r="U14" s="36" t="str">
+        <x:v>2026-07-01T00:09:02Z</x:v>
+      </x:c>
+      <x:c r="V14" s="36" t="str">
+        <x:v>2026-07-01T00:09:02Z</x:v>
+      </x:c>
+      <x:c r="W14" s="36" t="str">
+        <x:v>2026-07-02T00:09:02Z</x:v>
+      </x:c>
       <x:c r="X14" s="36"/>
       <x:c r="Y14" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z14" s="36" t="str">
-        <x:v>Migrated from GitHub issue #626; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c3</x:v>
       </x:c>
       <x:c r="AA14" s="36"/>
       <x:c r="AB14" s="36"/>
       <x:c r="AC14" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5651,7 +5651,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/dialog5.json</x:v>
       </x:c>
       <x:c r="Q20" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R20" s="36" t="str">
         <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c1</x:v>
@@ -5664,20 +5664,24 @@
         <x:v>2026-06-30T23:50:55Z</x:v>
       </x:c>
       <x:c r="V20" s="36" t="str">
-        <x:v>2026-06-30T23:50:55Z</x:v>
-      </x:c>
-      <x:c r="W20" s="36" t="str">
-        <x:v>2026-07-01T23:50:55Z</x:v>
-      </x:c>
-      <x:c r="X20" s="36"/>
+        <x:v>2026-07-01T00:33:19Z</x:v>
+      </x:c>
+      <x:c r="W20" s="36"/>
+      <x:c r="X20" s="36" t="str">
+        <x:v>2026-07-01T00:33:19Z</x:v>
+      </x:c>
       <x:c r="Y20" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z20" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c1</x:v>
-      </x:c>
-      <x:c r="AA20" s="36"/>
-      <x:c r="AB20" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA20" s="36" t="str">
+        <x:v>Relocated the single 'catacombs' map object (id 103) in res/maps/nouraajd/map.json from tile (22,17) next to cave1 to a reachable, unoccupied GrassTile at (57,103) east of the town wall; only x/y changed so the name-matched onDestroy trigger, holyRelic grant and Beren relic-return are unaffected. Dedicated catacombs art override already existed in config.json; cave1/cave2 untouched. Added NouraajdCatacombsContentTest and updated the topology golden (test_nouraajd_restored_map_layout_topology). Merged in PR #1138 (squash 3650252).</x:v>
+      </x:c>
+      <x:c r="AB20" s="36" t="str">
+        <x:v>CI green: native linux (GameTest map walkthrough incl. test_nouraajd_restored_map_layout_topology + nouraajd quest-state tests) passed; python3 -m unittest tests.test_content_validator = 124 tests OK. windows/coverage non-required and still running under slow CI.</x:v>
+      </x:c>
       <x:c r="AC20" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5481,7 +5481,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/dialog2.json</x:v>
       </x:c>
       <x:c r="Q18" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R18" s="36" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-28</x:v>
@@ -5494,20 +5494,24 @@
         <x:v>2026-07-01T00:01:55Z</x:v>
       </x:c>
       <x:c r="V18" s="36" t="str">
-        <x:v>2026-07-01T00:01:55Z</x:v>
-      </x:c>
-      <x:c r="W18" s="36" t="str">
-        <x:v>2026-07-01T02:01:55Z</x:v>
-      </x:c>
-      <x:c r="X18" s="36"/>
+        <x:v>2026-07-01T00:43:08Z</x:v>
+      </x:c>
+      <x:c r="W18" s="36"/>
+      <x:c r="X18" s="36" t="str">
+        <x:v>2026-07-01T00:43:08Z</x:v>
+      </x:c>
       <x:c r="Y18" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z18" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-28</x:v>
-      </x:c>
-      <x:c r="AA18" s="36"/>
-      <x:c r="AB18" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA18" s="36" t="str">
+        <x:v>Restored reliable conversations with oldWoman and questGiver. Root cause: both NPCs used CNpcRandomController and wandered off their exact trigger tiles, so onEnter dialog triggers fired unreliably. Changed only the oldWoman and questGiver controller definitions in res/maps/nouraajd/config.json from CNpcRandomController to the stationary CController, keeping exact IDs (oldWoman, questGiver, questDialog, questReturnDialog, dialog) intact so both NPCs stay on their trigger tiles and their dialog chains fire deterministically. Added a deterministic Nouraajd gameplay test exercising initial quest dialog, active reminder, amulet-return completion (once), questGiver OctoBogz dialog, no NPC-initiated combat, and save/load + repeated-approach stability. Merged via PR #1143.</x:v>
+      </x:c>
+      <x:c r="AB18" s="36" t="str">
+        <x:v>CI build workflow green on merge commit: validate, export, linux-fast, linux, windows-deps, windows all passed. New deterministic Nouraajd conversation test (test_nouraajd_oldwoman_questgiver_conversations_are_reliable) passes on linux and windows GameTest lanes.</x:v>
+      </x:c>
       <x:c r="AC18" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5133,7 +5133,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.h</x:v>
       </x:c>
       <x:c r="Q14" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R14" s="36" t="str">
         <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c3</x:v>
@@ -5146,20 +5146,24 @@
         <x:v>2026-07-01T00:09:02Z</x:v>
       </x:c>
       <x:c r="V14" s="36" t="str">
-        <x:v>2026-07-01T00:09:02Z</x:v>
-      </x:c>
-      <x:c r="W14" s="36" t="str">
-        <x:v>2026-07-02T00:09:02Z</x:v>
-      </x:c>
-      <x:c r="X14" s="36"/>
+        <x:v>2026-07-01T00:48:28Z</x:v>
+      </x:c>
+      <x:c r="W14" s="36"/>
+      <x:c r="X14" s="36" t="str">
+        <x:v>2026-07-01T00:48:28Z</x:v>
+      </x:c>
       <x:c r="Y14" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z14" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c3</x:v>
-      </x:c>
-      <x:c r="AA14" s="36"/>
-      <x:c r="AB14" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA14" s="36" t="str">
+        <x:v>Added a single canonical click-vs-drag threshold in CGui (Chebyshev max-axis distance, exclusive boundary, DRAG_MOVEMENT_THRESHOLD=4px) with a latched DragSession::dragActive flag; routed proxy lifecycle and all CListView drop/click/mouse-up decisions through it, so below-threshold jitter stays a click (no proxy, no drop, click fires once) and cancellation/window-leave/panel-removal clear candidate+active sessions. Also fixed the non-source mouse-up branch to consume the below-threshold release (was returning false after the threshold change). Merged in PR #1144 (squash 97d7bca).</x:v>
+      </x:c>
+      <x:c r="AB14" s="36" t="str">
+        <x:v>CI green: native linux + windows (ctest gui_unit_tests + gui_drag_proxy_unit_tests incl. new synthetic mouse-event tests: zero/below/boundary/above, negative axes, diagonal, accepted drop, cancellation, panel removal) passed. linux-coverage non-required/slow.</x:v>
+      </x:c>
       <x:c r="AC14" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5580,25 +5580,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/map.json</x:v>
       </x:c>
       <x:c r="Q19" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R19" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R19" s="39" t="str">
+        <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c4</x:v>
+      </x:c>
       <x:c r="S19" s="39"/>
-      <x:c r="T19" s="39"/>
-      <x:c r="U19" s="39"/>
-      <x:c r="V19" s="39"/>
-      <x:c r="W19" s="39"/>
+      <x:c r="T19" s="39" t="str">
+        <x:v>a82c8fa0-586b-4e73-8030-3c06073cf1e0</x:v>
+      </x:c>
+      <x:c r="U19" s="39" t="str">
+        <x:v>2026-07-01T00:52:18Z</x:v>
+      </x:c>
+      <x:c r="V19" s="39" t="str">
+        <x:v>2026-07-01T00:52:18Z</x:v>
+      </x:c>
+      <x:c r="W19" s="39" t="str">
+        <x:v>2026-07-02T00:52:18Z</x:v>
+      </x:c>
       <x:c r="X19" s="39"/>
       <x:c r="Y19" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z19" s="39" t="str">
-        <x:v>Migrated from GitHub issue #631; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c4</x:v>
       </x:c>
       <x:c r="AA19" s="39"/>
       <x:c r="AB19" s="39"/>
       <x:c r="AC19" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5580,7 +5580,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/maps/nouraajd/map.json</x:v>
       </x:c>
       <x:c r="Q19" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R19" s="39" t="str">
         <x:v>controller/ctrl-vm-31216-edb5360c/subagent-c4</x:v>
@@ -5593,20 +5593,24 @@
         <x:v>2026-07-01T00:52:18Z</x:v>
       </x:c>
       <x:c r="V19" s="39" t="str">
-        <x:v>2026-07-01T00:52:18Z</x:v>
-      </x:c>
-      <x:c r="W19" s="39" t="str">
-        <x:v>2026-07-02T00:52:18Z</x:v>
-      </x:c>
-      <x:c r="X19" s="39"/>
+        <x:v>2026-07-01T01:19:50Z</x:v>
+      </x:c>
+      <x:c r="W19" s="39"/>
+      <x:c r="X19" s="39" t="str">
+        <x:v>2026-07-01T01:19:50Z</x:v>
+      </x:c>
       <x:c r="Y19" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z19" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-31216-edb5360c/subagent-c4</x:v>
-      </x:c>
-      <x:c r="AA19" s="39"/>
-      <x:c r="AB19" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA19" s="39" t="str">
+        <x:v>State-branched the OctoBogz quest-giver dialogue on QuestSystem.get_state('octobogz_contract'): added contract_not_started/active/completed condition methods on OctoBogzDialog and split dialog2.json ENTRY into not_started-&gt;offer, active-&gt;ACTIVE_REMINDER (no accept), completed-&gt;COMPLETED_THANKS (no re-offer); the OFFER_HELP accept option is gated by contract_not_started. accept_quest retains its idempotent late-claim path so a contract completed before formal acceptance still pays the outstanding reward once (OCTOBOGZ_REWARD_CLAIMED guard). Trigger 'questGiver'/dialog id 'dialog' and reward guards preserved. Merged in PR #1155 (squash 27a6018).</x:v>
+      </x:c>
+      <x:c r="AB19" s="39" t="str">
+        <x:v>CI green: native linux passed test_nouraajd_quest_state_machine, test_nouraajd_octobogz_unique_reward_is_not_duplicated, and test_nouraajd_octobogz_late_contract_claims_existing_clear_reward (late reward-claim +1000 gold restored); tests.test_content_validator=124 OK statically verifies all dialog conditions/actions resolve and new states reachable. windows-deps/validate/linux-fast green; coverage skipped (content-only).</x:v>
+      </x:c>
       <x:c r="AC19" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5317,17 +5317,17 @@
         <x:v>2026-07-01T00:01:55Z</x:v>
       </x:c>
       <x:c r="V16" s="36" t="str">
-        <x:v>2026-07-01T00:01:55Z</x:v>
+        <x:v>2026-07-01T05:25:47Z</x:v>
       </x:c>
       <x:c r="W16" s="36" t="str">
-        <x:v>2026-07-01T02:01:55Z</x:v>
+        <x:v>2026-07-01T07:25:47Z</x:v>
       </x:c>
       <x:c r="X16" s="36"/>
       <x:c r="Y16" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z16" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-27</x:v>
+        <x:v>impl complete; PR #1141 open, awaiting CI unblock via test-shard fix #1164</x:v>
       </x:c>
       <x:c r="AA16" s="36"/>
       <x:c r="AB16" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5304,7 +5304,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/panel/CGameFightPanel.cpp</x:v>
       </x:c>
       <x:c r="Q16" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R16" s="36" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-27</x:v>
@@ -5317,20 +5317,24 @@
         <x:v>2026-07-01T00:01:55Z</x:v>
       </x:c>
       <x:c r="V16" s="36" t="str">
-        <x:v>2026-07-01T05:25:47Z</x:v>
-      </x:c>
-      <x:c r="W16" s="36" t="str">
-        <x:v>2026-07-01T07:25:47Z</x:v>
-      </x:c>
-      <x:c r="X16" s="36"/>
+        <x:v>2026-07-01T11:30:57Z</x:v>
+      </x:c>
+      <x:c r="W16" s="36"/>
+      <x:c r="X16" s="36" t="str">
+        <x:v>2026-07-01T11:30:57Z</x:v>
+      </x:c>
       <x:c r="Y16" s="36" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z16" s="36" t="str">
-        <x:v>impl complete; PR #1141 open, awaiting CI unblock via test-shard fix #1164</x:v>
-      </x:c>
-      <x:c r="AA16" s="36"/>
-      <x:c r="AB16" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA16" s="36" t="str">
+        <x:v>Merged in PR #1141: rewrote CGameInventoryPanel::inventoryRightClickCallback to call player-&gt;useItem via usable_item/inventory_player helpers, mirroring the fight panel; +tests in test_gui.cpp.</x:v>
+      </x:c>
+      <x:c r="AB16" s="36" t="str">
+        <x:v>CI green on merge (validate/export/linux-fast/linux/windows). gui_unit_tests cover use+consume, quest-item protection, drag-still-starts.</x:v>
+      </x:c>
       <x:c r="AC16" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5769,30 +5769,22 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/AGENTS.md</x:v>
       </x:c>
       <x:c r="Q21" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="R21" s="39" t="str">
-        <x:v>controller/ctrl-vm-4026-9b5a29b5/subagent-5</x:v>
-      </x:c>
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R21" s="39"/>
       <x:c r="S21" s="39"/>
-      <x:c r="T21" s="39" t="str">
-        <x:v>4d74f425-a323-41d6-931b-13cf0d913a14</x:v>
-      </x:c>
-      <x:c r="U21" s="39" t="str">
-        <x:v>2026-06-30T11:06:18Z</x:v>
-      </x:c>
+      <x:c r="T21" s="39"/>
+      <x:c r="U21" s="39"/>
       <x:c r="V21" s="39" t="str">
-        <x:v>2026-06-30T12:22:37Z</x:v>
-      </x:c>
-      <x:c r="W21" s="39" t="str">
-        <x:v>2026-07-01T12:22:37Z</x:v>
-      </x:c>
+        <x:v>2026-07-01T16:15:09Z</x:v>
+      </x:c>
+      <x:c r="W21" s="39"/>
       <x:c r="X21" s="39"/>
       <x:c r="Y21" s="39" t="n">
-        <x:v>90</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z21" s="39" t="str">
-        <x:v>Implementation complete and pushed; blocked only on main-red native CI (test_scene_manager_transition_requested_during_combat_preserves_source_map, a pre-existing combat-transition regression on main, observed 05b033bd). Do not reclaim. awaiting user review of authority-machinery PR #934.</x:v>
+        <x:v>Stale claim reclaimed from controller/ctrl-vm-4026-9b5a29b5/subagent-5; prior claim 4d74f425-a323-41d6-931b-13cf0d913a14</x:v>
       </x:c>
       <x:c r="AA21" s="39"/>
       <x:c r="AB21" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5850,30 +5850,22 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/game.py</x:v>
       </x:c>
       <x:c r="Q22" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="R22" s="36" t="str">
-        <x:v>controller/ctrl-vm-4024-7534d796/subagent-10</x:v>
-      </x:c>
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R22" s="36"/>
       <x:c r="S22" s="36"/>
-      <x:c r="T22" s="36" t="str">
-        <x:v>866b9190-9672-423a-84e6-7a89992a38e3</x:v>
-      </x:c>
-      <x:c r="U22" s="36" t="str">
-        <x:v>2026-06-30T20:07:26Z</x:v>
-      </x:c>
+      <x:c r="T22" s="36"/>
+      <x:c r="U22" s="36"/>
       <x:c r="V22" s="36" t="str">
-        <x:v>2026-06-30T20:07:26Z</x:v>
-      </x:c>
-      <x:c r="W22" s="36" t="str">
-        <x:v>2026-07-01T20:07:26Z</x:v>
-      </x:c>
+        <x:v>2026-07-01T20:13:02Z</x:v>
+      </x:c>
+      <x:c r="W22" s="36"/>
       <x:c r="X22" s="36"/>
       <x:c r="Y22" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z22" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-10</x:v>
+        <x:v>Stale claim reclaimed from controller/ctrl-vm-4024-7534d796/subagent-10; prior claim 866b9190-9672-423a-84e6-7a89992a38e3</x:v>
       </x:c>
       <x:c r="AA22" s="36"/>
       <x:c r="AB22" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6114,30 +6114,22 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/vcpkg triplets/manifests</x:v>
       </x:c>
       <x:c r="Q25" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
-      </x:c>
-      <x:c r="R25" s="39" t="str">
-        <x:v>controller/ctrl-vm-4024-7534d796/subagent-11</x:v>
-      </x:c>
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R25" s="39"/>
       <x:c r="S25" s="39"/>
-      <x:c r="T25" s="39" t="str">
-        <x:v>ff73ecb2-7600-431d-92ba-da44273f9606</x:v>
-      </x:c>
-      <x:c r="U25" s="39" t="str">
-        <x:v>2026-06-30T20:15:07Z</x:v>
-      </x:c>
+      <x:c r="T25" s="39"/>
+      <x:c r="U25" s="39"/>
       <x:c r="V25" s="39" t="str">
-        <x:v>2026-06-30T20:15:07Z</x:v>
-      </x:c>
-      <x:c r="W25" s="39" t="str">
-        <x:v>2026-07-01T20:15:07Z</x:v>
-      </x:c>
+        <x:v>2026-07-01T20:17:34Z</x:v>
+      </x:c>
+      <x:c r="W25" s="39"/>
       <x:c r="X25" s="39"/>
       <x:c r="Y25" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z25" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4024-7534d796/subagent-11</x:v>
+        <x:v>Stale claim reclaimed from controller/ctrl-vm-4024-7534d796/subagent-11; prior claim ff73ecb2-7600-431d-92ba-da44273f9606</x:v>
       </x:c>
       <x:c r="AA25" s="39"/>
       <x:c r="AB25" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5769,27 +5769,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/AGENTS.md</x:v>
       </x:c>
       <x:c r="Q21" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R21" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R21" s="39" t="str">
+        <x:v>ctrl-vm-2256-06ac44fc</x:v>
+      </x:c>
       <x:c r="S21" s="39"/>
-      <x:c r="T21" s="39"/>
-      <x:c r="U21" s="39"/>
+      <x:c r="T21" s="39" t="str">
+        <x:v>5a8f6b65-9460-4e5c-98aa-d1c57420b18f</x:v>
+      </x:c>
+      <x:c r="U21" s="39" t="str">
+        <x:v>2026-07-02T07:46:27Z</x:v>
+      </x:c>
       <x:c r="V21" s="39" t="str">
-        <x:v>2026-07-01T16:15:09Z</x:v>
-      </x:c>
-      <x:c r="W21" s="39"/>
+        <x:v>2026-07-02T07:46:39Z</x:v>
+      </x:c>
+      <x:c r="W21" s="39" t="str">
+        <x:v>2026-07-02T09:46:39Z</x:v>
+      </x:c>
       <x:c r="X21" s="39"/>
       <x:c r="Y21" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z21" s="39" t="str">
-        <x:v>Stale claim reclaimed from controller/ctrl-vm-4026-9b5a29b5/subagent-5; prior claim 4d74f425-a323-41d6-931b-13cf0d913a14</x:v>
+        <x:v>Implemented run-identity ambiguity + attempt binding in poll_pr_checks.py; PR #1261 open (fast-path CI green, 7 tests). Authority-file change awaits human review + native-green.</x:v>
       </x:c>
       <x:c r="AA21" s="39"/>
       <x:c r="AB21" s="39"/>
       <x:c r="AC21" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72" customHeight="1">
@@ -5850,27 +5858,39 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/res/game.py</x:v>
       </x:c>
       <x:c r="Q22" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R22" s="36"/>
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="R22" s="36" t="str">
+        <x:v>ctrl-vm-2256-06ac44fc</x:v>
+      </x:c>
       <x:c r="S22" s="36"/>
-      <x:c r="T22" s="36"/>
-      <x:c r="U22" s="36"/>
+      <x:c r="T22" s="36" t="str">
+        <x:v>0a6bfa03-b5e8-4d7b-a7ee-f64508429e8c</x:v>
+      </x:c>
+      <x:c r="U22" s="36" t="str">
+        <x:v>2026-07-02T07:45:52Z</x:v>
+      </x:c>
       <x:c r="V22" s="36" t="str">
-        <x:v>2026-07-01T20:13:02Z</x:v>
+        <x:v>2026-07-02T07:46:26Z</x:v>
       </x:c>
       <x:c r="W22" s="36"/>
-      <x:c r="X22" s="36"/>
+      <x:c r="X22" s="36" t="str">
+        <x:v>2026-07-02T07:46:26Z</x:v>
+      </x:c>
       <x:c r="Y22" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z22" s="36" t="str">
-        <x:v>Stale claim reclaimed from controller/ctrl-vm-4024-7534d796/subagent-10; prior claim 866b9190-9672-423a-84e6-7a89992a38e3</x:v>
-      </x:c>
-      <x:c r="AA22" s="36"/>
-      <x:c r="AB22" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA22" s="36" t="str">
+        <x:v>Already satisfied by #1063 (commit 483d1dc): docs/design/plugin_trust_boundary.md documents the trust model; CLoader.cpp enforces restricted plugin builtins, a game/json-only import allowlist, and resource-root path validation that rejects absolute/parent-traversal paths and plugins outside trusted roots. Reconciling stale NOT_STARTED row to DONE.</x:v>
+      </x:c>
+      <x:c r="AB22" s="36" t="str">
+        <x:v>python3 -m unittest tests.security.test_python_plugin_sandbox -&gt; Ran 8 tests, OK (restricted builtins, import allowlist, path-traversal rejection, trust-boundary doc present, trusted crafting plugin still loads via resource provider).</x:v>
+      </x:c>
       <x:c r="AC22" s="36" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -6134,27 +6134,39 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/vcpkg triplets/manifests</x:v>
       </x:c>
       <x:c r="Q25" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R25" s="39"/>
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="R25" s="39" t="str">
+        <x:v>ctrl-vm-2256-06ac44fc</x:v>
+      </x:c>
       <x:c r="S25" s="39"/>
-      <x:c r="T25" s="39"/>
-      <x:c r="U25" s="39"/>
+      <x:c r="T25" s="39" t="str">
+        <x:v>9f2d6cae-5763-4e1a-897b-24bfcc42c8a1</x:v>
+      </x:c>
+      <x:c r="U25" s="39" t="str">
+        <x:v>2026-07-02T07:49:14Z</x:v>
+      </x:c>
       <x:c r="V25" s="39" t="str">
-        <x:v>2026-07-01T20:17:34Z</x:v>
+        <x:v>2026-07-02T07:49:14Z</x:v>
       </x:c>
       <x:c r="W25" s="39"/>
-      <x:c r="X25" s="39"/>
+      <x:c r="X25" s="39" t="str">
+        <x:v>2026-07-02T07:49:14Z</x:v>
+      </x:c>
       <x:c r="Y25" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z25" s="39" t="str">
-        <x:v>Stale claim reclaimed from controller/ctrl-vm-4024-7534d796/subagent-11; prior claim ff73ecb2-7600-431d-92ba-da44273f9606</x:v>
-      </x:c>
-      <x:c r="AA25" s="39"/>
-      <x:c r="AB25" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA25" s="39" t="str">
+        <x:v>Already satisfied by #1064 (commit 4f9074a): Windows CI sets up trusted fast-tools (sccache) in RUNNER_TEMP outside the PR workspace, hash-verifies the sccache archive unconditionally (a pre-existing workspace sccache.exe cannot short-circuit it) and invokes it by verified absolute path; the vcpkg installed tree is validated/reinstalled when the cache is incomplete and the cache key includes dependency-defining inputs. Reconciling stale NOT_STARTED row to DONE.</x:v>
+      </x:c>
+      <x:c r="AB25" s="39" t="str">
+        <x:v>python3 -m unittest tests.security.test_configure_supply_chain -&gt; Ran 15 tests, OK (tools outside workspace, unconditional sccache hash verify, vcpkg cache validation + dependency-input cache key, pinned action SHAs).</x:v>
+      </x:c>
       <x:c r="AC25" s="39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5226,25 +5226,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.cpp</x:v>
       </x:c>
       <x:c r="Q15" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R15" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R15" s="39" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-37</x:v>
+      </x:c>
       <x:c r="S15" s="39"/>
-      <x:c r="T15" s="39"/>
-      <x:c r="U15" s="39"/>
-      <x:c r="V15" s="39"/>
-      <x:c r="W15" s="39"/>
+      <x:c r="T15" s="39" t="str">
+        <x:v>9af78786-65ba-4911-99cb-a06a32157a02</x:v>
+      </x:c>
+      <x:c r="U15" s="39" t="str">
+        <x:v>2026-07-02T10:15:14Z</x:v>
+      </x:c>
+      <x:c r="V15" s="39" t="str">
+        <x:v>2026-07-02T10:15:14Z</x:v>
+      </x:c>
+      <x:c r="W15" s="39" t="str">
+        <x:v>2026-07-02T14:15:14Z</x:v>
+      </x:c>
       <x:c r="X15" s="39"/>
       <x:c r="Y15" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" s="39" t="str">
-        <x:v>Migrated from GitHub issue #627; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-37</x:v>
       </x:c>
       <x:c r="AA15" s="39"/>
       <x:c r="AB15" s="39"/>
       <x:c r="AC15" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4246,25 +4246,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q3" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R3" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R3" s="39" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-1</x:v>
+      </x:c>
       <x:c r="S3" s="39"/>
-      <x:c r="T3" s="39"/>
-      <x:c r="U3" s="39"/>
-      <x:c r="V3" s="39"/>
-      <x:c r="W3" s="39"/>
+      <x:c r="T3" s="39" t="str">
+        <x:v>defd0016-bfb4-4d45-a574-496d5bf2992c</x:v>
+      </x:c>
+      <x:c r="U3" s="39" t="str">
+        <x:v>2026-07-02T11:49:02Z</x:v>
+      </x:c>
+      <x:c r="V3" s="39" t="str">
+        <x:v>2026-07-02T11:49:02Z</x:v>
+      </x:c>
+      <x:c r="W3" s="39" t="str">
+        <x:v>2026-07-02T13:49:02Z</x:v>
+      </x:c>
       <x:c r="X3" s="39"/>
       <x:c r="Y3" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z3" s="39" t="str">
-        <x:v>Migrated from GitHub issue #615; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-1</x:v>
       </x:c>
       <x:c r="AA3" s="39"/>
       <x:c r="AB3" s="39"/>
       <x:c r="AC3" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4969,25 +4969,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/GitHub snapshot builder/controller guidance</x:v>
       </x:c>
       <x:c r="Q12" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R12" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R12" s="36" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-3</x:v>
+      </x:c>
       <x:c r="S12" s="36"/>
-      <x:c r="T12" s="36"/>
-      <x:c r="U12" s="36"/>
-      <x:c r="V12" s="36"/>
-      <x:c r="W12" s="36"/>
+      <x:c r="T12" s="36" t="str">
+        <x:v>36ce0bab-d2a3-4d86-86df-029511667f2c</x:v>
+      </x:c>
+      <x:c r="U12" s="36" t="str">
+        <x:v>2026-07-02T12:03:02Z</x:v>
+      </x:c>
+      <x:c r="V12" s="36" t="str">
+        <x:v>2026-07-02T12:03:02Z</x:v>
+      </x:c>
+      <x:c r="W12" s="36" t="str">
+        <x:v>2026-07-02T14:03:02Z</x:v>
+      </x:c>
       <x:c r="X12" s="36"/>
       <x:c r="Y12" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z12" s="36" t="str">
-        <x:v>Migrated from GitHub issue #624; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-3</x:v>
       </x:c>
       <x:c r="AA12" s="36"/>
       <x:c r="AB12" s="36"/>
       <x:c r="AC12" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4335,25 +4335,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q4" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R4" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R4" s="36" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-4</x:v>
+      </x:c>
       <x:c r="S4" s="36"/>
-      <x:c r="T4" s="36"/>
-      <x:c r="U4" s="36"/>
-      <x:c r="V4" s="36"/>
-      <x:c r="W4" s="36"/>
+      <x:c r="T4" s="36" t="str">
+        <x:v>880b1760-0eb6-4f45-b1a4-016d14b2ea37</x:v>
+      </x:c>
+      <x:c r="U4" s="36" t="str">
+        <x:v>2026-07-02T12:06:09Z</x:v>
+      </x:c>
+      <x:c r="V4" s="36" t="str">
+        <x:v>2026-07-02T12:06:09Z</x:v>
+      </x:c>
+      <x:c r="W4" s="36" t="str">
+        <x:v>2026-07-02T14:06:09Z</x:v>
+      </x:c>
       <x:c r="X4" s="36"/>
       <x:c r="Y4" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z4" s="36" t="str">
-        <x:v>Migrated from GitHub issue #616; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-4</x:v>
       </x:c>
       <x:c r="AA4" s="36"/>
       <x:c r="AB4" s="36"/>
       <x:c r="AC4" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5269,17 +5269,17 @@
         <x:v>2026-07-02T10:15:14Z</x:v>
       </x:c>
       <x:c r="V15" s="39" t="str">
-        <x:v>2026-07-02T10:15:14Z</x:v>
+        <x:v>2026-07-02T12:28:50Z</x:v>
       </x:c>
       <x:c r="W15" s="39" t="str">
-        <x:v>2026-07-02T14:15:14Z</x:v>
+        <x:v>2026-07-02T16:28:50Z</x:v>
       </x:c>
       <x:c r="X15" s="39"/>
       <x:c r="Y15" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z15" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-37</x:v>
+        <x:v>impl complete; PR #1272 open, blocked by fleet-wide red main (ninemarches/sunderedmarch walkthroughs + SIGABRT teardown); merge on main recovery</x:v>
       </x:c>
       <x:c r="AA15" s="39"/>
       <x:c r="AB15" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4259,17 +4259,17 @@
         <x:v>2026-07-02T11:49:02Z</x:v>
       </x:c>
       <x:c r="V3" s="39" t="str">
-        <x:v>2026-07-02T11:49:02Z</x:v>
+        <x:v>2026-07-02T12:57:38Z</x:v>
       </x:c>
       <x:c r="W3" s="39" t="str">
-        <x:v>2026-07-02T13:49:02Z</x:v>
+        <x:v>2026-07-02T14:57:38Z</x:v>
       </x:c>
       <x:c r="X3" s="39"/>
       <x:c r="Y3" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z3" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-1</x:v>
+        <x:v>Implementation complete; PR #1277 open, awaiting green CI after main fix #1274 merges</x:v>
       </x:c>
       <x:c r="AA3" s="39"/>
       <x:c r="AB3" s="39"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4992,17 +4992,17 @@
         <x:v>2026-07-02T12:03:02Z</x:v>
       </x:c>
       <x:c r="V12" s="36" t="str">
-        <x:v>2026-07-02T12:03:02Z</x:v>
+        <x:v>2026-07-02T12:59:01Z</x:v>
       </x:c>
       <x:c r="W12" s="36" t="str">
-        <x:v>2026-07-02T14:03:02Z</x:v>
+        <x:v>2026-07-02T14:59:01Z</x:v>
       </x:c>
       <x:c r="X12" s="36"/>
       <x:c r="Y12" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z12" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-3</x:v>
+        <x:v>Implementation complete; PR #1279 open, awaiting green CI after main fix #1274 merges</x:v>
       </x:c>
       <x:c r="AA12" s="36"/>
       <x:c r="AB12" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4348,17 +4348,17 @@
         <x:v>2026-07-02T12:06:09Z</x:v>
       </x:c>
       <x:c r="V4" s="36" t="str">
-        <x:v>2026-07-02T12:06:09Z</x:v>
+        <x:v>2026-07-02T12:59:44Z</x:v>
       </x:c>
       <x:c r="W4" s="36" t="str">
-        <x:v>2026-07-02T14:06:09Z</x:v>
+        <x:v>2026-07-02T14:59:44Z</x:v>
       </x:c>
       <x:c r="X4" s="36"/>
       <x:c r="Y4" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Z4" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-4</x:v>
+        <x:v>Implementation complete; PR #1280 open, awaiting green CI after main fix #1274 merges</x:v>
       </x:c>
       <x:c r="AA4" s="36"/>
       <x:c r="AB4" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4979,7 +4979,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/GitHub snapshot builder/controller guidance</x:v>
       </x:c>
       <x:c r="Q12" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R12" s="36" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-3</x:v>
@@ -4992,20 +4992,24 @@
         <x:v>2026-07-02T12:03:02Z</x:v>
       </x:c>
       <x:c r="V12" s="36" t="str">
-        <x:v>2026-07-02T12:59:01Z</x:v>
-      </x:c>
-      <x:c r="W12" s="36" t="str">
-        <x:v>2026-07-02T14:59:01Z</x:v>
-      </x:c>
-      <x:c r="X12" s="36"/>
+        <x:v>2026-07-02T14:34:30Z</x:v>
+      </x:c>
+      <x:c r="W12" s="36"/>
+      <x:c r="X12" s="36" t="str">
+        <x:v>2026-07-02T14:34:30Z</x:v>
+      </x:c>
       <x:c r="Y12" s="36" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z12" s="36" t="str">
-        <x:v>Implementation complete; PR #1279 open, awaiting green CI after main fix #1274 merges</x:v>
-      </x:c>
-      <x:c r="AA12" s="36"/>
-      <x:c r="AB12" s="36"/>
+        <x:v>DONE via PR #1279</x:v>
+      </x:c>
+      <x:c r="AA12" s="36" t="str">
+        <x:v>Merged PR #1279 (squash 9a11bd3). pr_review_audit now normalizes checks with (kind, app, workflow, name) identity, deterministic timestamp/attempt/run-id ordering, conservative ambiguity flagging, and additive ignoredStale/ambiguous output; summaries derive from effective attempts only.</x:v>
+      </x:c>
+      <x:c r="AB12" s="36" t="str">
+        <x:v>python3 -m unittest tests.test_pr_review_audit (41 OK); tests.test_poll_pr_checks (39 OK); py_compile; test.py --suite fast (9 OK); black --check clean; PR #1279 CI linux green (lightweight class)</x:v>
+      </x:c>
       <x:c r="AC12" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5260,7 +5260,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/src/gui/CGui.cpp</x:v>
       </x:c>
       <x:c r="Q15" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R15" s="39" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-37</x:v>
@@ -5273,20 +5273,24 @@
         <x:v>2026-07-02T10:15:14Z</x:v>
       </x:c>
       <x:c r="V15" s="39" t="str">
-        <x:v>2026-07-02T12:28:50Z</x:v>
-      </x:c>
-      <x:c r="W15" s="39" t="str">
-        <x:v>2026-07-02T16:28:50Z</x:v>
-      </x:c>
-      <x:c r="X15" s="39"/>
+        <x:v>2026-07-02T15:18:19Z</x:v>
+      </x:c>
+      <x:c r="W15" s="39"/>
+      <x:c r="X15" s="39" t="str">
+        <x:v>2026-07-02T15:18:19Z</x:v>
+      </x:c>
       <x:c r="Y15" s="39" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z15" s="39" t="str">
-        <x:v>impl complete; PR #1272 open, blocked by fleet-wide red main (ninemarches/sunderedmarch walkthroughs + SIGABRT teardown); merge on main recovery</x:v>
-      </x:c>
-      <x:c r="AA15" s="39"/>
-      <x:c r="AB15" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA15" s="39" t="str">
+        <x:v>Merged in PR #1272: payload-only drop semantics in CListView (removed legacy click-callback fallback on moved cross-list drops); exact dragged item equips; quest/incompatible/same-list/cancel paths inert; +6 tests in test_gui.cpp.</x:v>
+      </x:c>
+      <x:c r="AB15" s="39" t="str">
+        <x:v>CI green on merge.</x:v>
+      </x:c>
       <x:c r="AC15" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4246,7 +4246,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q3" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R3" s="39" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-1</x:v>
@@ -4259,20 +4259,24 @@
         <x:v>2026-07-02T11:49:02Z</x:v>
       </x:c>
       <x:c r="V3" s="39" t="str">
-        <x:v>2026-07-02T12:57:38Z</x:v>
-      </x:c>
-      <x:c r="W3" s="39" t="str">
-        <x:v>2026-07-02T14:57:38Z</x:v>
-      </x:c>
-      <x:c r="X3" s="39"/>
+        <x:v>2026-07-02T15:25:01Z</x:v>
+      </x:c>
+      <x:c r="W3" s="39"/>
+      <x:c r="X3" s="39" t="str">
+        <x:v>2026-07-02T15:25:01Z</x:v>
+      </x:c>
       <x:c r="Y3" s="39" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z3" s="39" t="str">
-        <x:v>Implementation complete; PR #1277 open, awaiting green CI after main fix #1274 merges</x:v>
-      </x:c>
-      <x:c r="AA3" s="39"/>
-      <x:c r="AB3" s="39"/>
+        <x:v>DONE via PR #1277</x:v>
+      </x:c>
+      <x:c r="AA3" s="39" t="str">
+        <x:v>Merged PR #1277 (squash 5c16a5d). Adds scripts/write_leases.py: JSON write-lease store separate from XLSX claims with acquire/renew/release/recover/list/validate, atomic all-or-nothing batches under a sidecar lock, confidence-ranked scope normalization and deterministic coupled-area expansion; conflicting ACTIVE scopes cannot both write; recovery is lease-lifecycle-only. Docs sections added; 27 tests.</x:v>
+      </x:c>
+      <x:c r="AB3" s="39" t="str">
+        <x:v>tests.test_write_leases (27 OK); tests.test_issue_queue (45 OK); doc-guard suites (58 OK); queue validates clean; PR #1277 CI green (linux, windows-deps, windows)</x:v>
+      </x:c>
       <x:c r="AC3" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4352,17 +4352,17 @@
         <x:v>2026-07-02T12:06:09Z</x:v>
       </x:c>
       <x:c r="V4" s="36" t="str">
-        <x:v>2026-07-02T12:59:44Z</x:v>
+        <x:v>2026-07-02T15:26:03Z</x:v>
       </x:c>
       <x:c r="W4" s="36" t="str">
-        <x:v>2026-07-02T14:59:44Z</x:v>
+        <x:v>2026-07-02T17:26:03Z</x:v>
       </x:c>
       <x:c r="X4" s="36"/>
       <x:c r="Y4" s="36" t="n">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Z4" s="36" t="str">
-        <x:v>Implementation complete; PR #1280 open, awaiting green CI after main fix #1274 merges</x:v>
+        <x:v>PR #1280 green on prior head; revalidating after #1277 merge, completion imminent</x:v>
       </x:c>
       <x:c r="AA4" s="36"/>
       <x:c r="AB4" s="36"/>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4427,25 +4427,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/docs/codex-agent-queue.md</x:v>
       </x:c>
       <x:c r="Q5" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R5" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R5" s="39" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-5</x:v>
+      </x:c>
       <x:c r="S5" s="39"/>
-      <x:c r="T5" s="39"/>
-      <x:c r="U5" s="39"/>
-      <x:c r="V5" s="39"/>
-      <x:c r="W5" s="39"/>
+      <x:c r="T5" s="39" t="str">
+        <x:v>846a39f7-c64a-4415-a598-be35926f2616</x:v>
+      </x:c>
+      <x:c r="U5" s="39" t="str">
+        <x:v>2026-07-02T15:26:43Z</x:v>
+      </x:c>
+      <x:c r="V5" s="39" t="str">
+        <x:v>2026-07-02T15:26:43Z</x:v>
+      </x:c>
+      <x:c r="W5" s="39" t="str">
+        <x:v>2026-07-02T17:26:43Z</x:v>
+      </x:c>
       <x:c r="X5" s="39"/>
       <x:c r="Y5" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z5" s="39" t="str">
-        <x:v>Migrated from GitHub issue #617; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-5</x:v>
       </x:c>
       <x:c r="AA5" s="39"/>
       <x:c r="AB5" s="39"/>
       <x:c r="AC5" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4597,25 +4597,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/poll_pr_checks.py</x:v>
       </x:c>
       <x:c r="Q7" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R7" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R7" s="39" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-6</x:v>
+      </x:c>
       <x:c r="S7" s="39"/>
-      <x:c r="T7" s="39"/>
-      <x:c r="U7" s="39"/>
-      <x:c r="V7" s="39"/>
-      <x:c r="W7" s="39"/>
+      <x:c r="T7" s="39" t="str">
+        <x:v>b10fbae1-9510-4bf1-9c8b-6e49e658b0e8</x:v>
+      </x:c>
+      <x:c r="U7" s="39" t="str">
+        <x:v>2026-07-02T15:27:34Z</x:v>
+      </x:c>
+      <x:c r="V7" s="39" t="str">
+        <x:v>2026-07-02T15:27:34Z</x:v>
+      </x:c>
+      <x:c r="W7" s="39" t="str">
+        <x:v>2026-07-02T17:27:34Z</x:v>
+      </x:c>
       <x:c r="X7" s="39"/>
       <x:c r="Y7" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z7" s="39" t="str">
-        <x:v>Migrated from GitHub issue #619; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-6</x:v>
       </x:c>
       <x:c r="AA7" s="39"/>
       <x:c r="AB7" s="39"/>
       <x:c r="AC7" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4339,7 +4339,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q4" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R4" s="36" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-4</x:v>
@@ -4352,20 +4352,24 @@
         <x:v>2026-07-02T12:06:09Z</x:v>
       </x:c>
       <x:c r="V4" s="36" t="str">
-        <x:v>2026-07-02T15:26:03Z</x:v>
-      </x:c>
-      <x:c r="W4" s="36" t="str">
-        <x:v>2026-07-02T17:26:03Z</x:v>
-      </x:c>
-      <x:c r="X4" s="36"/>
+        <x:v>2026-07-02T15:50:57Z</x:v>
+      </x:c>
+      <x:c r="W4" s="36"/>
+      <x:c r="X4" s="36" t="str">
+        <x:v>2026-07-02T15:50:57Z</x:v>
+      </x:c>
       <x:c r="Y4" s="36" t="n">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z4" s="36" t="str">
-        <x:v>PR #1280 green on prior head; revalidating after #1277 merge, completion imminent</x:v>
-      </x:c>
-      <x:c r="AA4" s="36"/>
-      <x:c r="AB4" s="36"/>
+        <x:v>DONE via PR #1280</x:v>
+      </x:c>
+      <x:c r="AA4" s="36" t="str">
+        <x:v>Merged PR #1280 (squash bf3a8ac). Adds scripts/subagent_registry.py: versioned controller-local lifecycle registry (register/report/finalize/list/sweep/mark/validate) with atomic locked persistence; strictly read-only byte-stable sweeper reconciling records against worktree/branch/workbook-claim evidence with ORPHANED/UNREACHABLE recommendations; 16 tests; docs sections.</x:v>
+      </x:c>
+      <x:c r="AB4" s="36" t="str">
+        <x:v>tests.test_subagent_registry (16 OK); tests.test_issue_queue (45 OK); doc guards (58 OK); PR #1280 CI green (linux, windows-deps, windows)</x:v>
+      </x:c>
       <x:c r="AC4" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4769,25 +4769,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/prompts/codex-workflow-optimizer.md</x:v>
       </x:c>
       <x:c r="Q9" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R9" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R9" s="39" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
+      </x:c>
       <x:c r="S9" s="39"/>
-      <x:c r="T9" s="39"/>
-      <x:c r="U9" s="39"/>
-      <x:c r="V9" s="39"/>
-      <x:c r="W9" s="39"/>
+      <x:c r="T9" s="39" t="str">
+        <x:v>7920ae34-aaca-4808-a308-adfcd6e0f3e3</x:v>
+      </x:c>
+      <x:c r="U9" s="39" t="str">
+        <x:v>2026-07-02T15:55:04Z</x:v>
+      </x:c>
+      <x:c r="V9" s="39" t="str">
+        <x:v>2026-07-02T15:55:04Z</x:v>
+      </x:c>
+      <x:c r="W9" s="39" t="str">
+        <x:v>2026-07-02T17:55:04Z</x:v>
+      </x:c>
       <x:c r="X9" s="39"/>
       <x:c r="Y9" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z9" s="39" t="str">
-        <x:v>Migrated from GitHub issue #621; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
       </x:c>
       <x:c r="AA9" s="39"/>
       <x:c r="AB9" s="39"/>
       <x:c r="AC9" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4431,7 +4431,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/docs/codex-agent-queue.md</x:v>
       </x:c>
       <x:c r="Q5" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R5" s="39" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-5</x:v>
@@ -4444,20 +4444,24 @@
         <x:v>2026-07-02T15:26:43Z</x:v>
       </x:c>
       <x:c r="V5" s="39" t="str">
-        <x:v>2026-07-02T15:26:43Z</x:v>
-      </x:c>
-      <x:c r="W5" s="39" t="str">
-        <x:v>2026-07-02T17:26:43Z</x:v>
-      </x:c>
-      <x:c r="X5" s="39"/>
+        <x:v>2026-07-02T17:35:04Z</x:v>
+      </x:c>
+      <x:c r="W5" s="39"/>
+      <x:c r="X5" s="39" t="str">
+        <x:v>2026-07-02T17:35:04Z</x:v>
+      </x:c>
       <x:c r="Y5" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z5" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-5</x:v>
-      </x:c>
-      <x:c r="AA5" s="39"/>
-      <x:c r="AB5" s="39"/>
+        <x:v>Completed by controller ctrl-vm-4027-c0afa077 after squash-merge of PR #1306.</x:v>
+      </x:c>
+      <x:c r="AA5" s="39" t="str">
+        <x:v>Implemented by PR #1306 (squash-merged as 9e11e8a6): scripts/resource_broker.py observation/reservation split (read-only probes for memory, heavy jobs, Xvfb displays, TCP ports, build-dir ownership, MCP slots; typed atomic all-or-nothing reservations in planning/resource_reservations.json with sidecar lock, exclusive-conflict exit 3, non-destructive recover), controller_resource_audit.py subcommand dispatch with additive JSON, docs sections in AGENTS.md / docs/codex-agent-queue.md / prompts/codex-queue-controller.md.</x:v>
+      </x:c>
+      <x:c r="AB5" s="39" t="str">
+        <x:v>tests.test_controller_resource_audit 56 OK; controller_resource_audit --json exit 0 additive; tests.test_prompt_inventory + tests.test_workbook_queue 58 OK; py_compile OK; test.py --suite fast OK; black -l 120 clean; indentation clean. CI: pull_request build run 28608713362 on PR head 28cc1238 concluded success (after rebase onto main's paper.png configure fix).</x:v>
+      </x:c>
       <x:c r="AC5" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4605,7 +4605,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/poll_pr_checks.py</x:v>
       </x:c>
       <x:c r="Q7" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R7" s="39" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-6</x:v>
@@ -4618,20 +4618,24 @@
         <x:v>2026-07-02T15:27:34Z</x:v>
       </x:c>
       <x:c r="V7" s="39" t="str">
-        <x:v>2026-07-02T15:27:34Z</x:v>
-      </x:c>
-      <x:c r="W7" s="39" t="str">
-        <x:v>2026-07-02T17:27:34Z</x:v>
-      </x:c>
-      <x:c r="X7" s="39"/>
+        <x:v>2026-07-02T17:42:22Z</x:v>
+      </x:c>
+      <x:c r="W7" s="39"/>
+      <x:c r="X7" s="39" t="str">
+        <x:v>2026-07-02T17:42:22Z</x:v>
+      </x:c>
       <x:c r="Y7" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z7" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-6</x:v>
-      </x:c>
-      <x:c r="AA7" s="39"/>
-      <x:c r="AB7" s="39"/>
+        <x:v>Completed by controller ctrl-vm-4027-c0afa077 after squash-merge of PR #1307.</x:v>
+      </x:c>
+      <x:c r="AA7" s="39" t="str">
+        <x:v>Implemented by PR #1307 (squash-merged as 3f5d16ba): scripts/controller_capability_probe.py read-only capability snapshot (repository/github/ci/toolchain/build/agent sections, available/unavailable/unknown/unsupported statuses, redacted bounded evidence, deterministic sorted output, --now injection, exit 0 on missing capabilities), doc guidance to treat unknown/unavailable required capabilities as dispatch blockers. Validation-authority files untouched.</x:v>
+      </x:c>
+      <x:c r="AB7" s="39" t="str">
+        <x:v>tests.test_controller_capability_probe 28 OK; probe --json byte-identical across two runs, exit 0; tests.test_prompt_inventory + tests.test_workbook_queue 58 OK; py_compile OK; test.py --suite fast OK; black -l 120 clean; indentation clean. CI: pull_request build run 28608714582 on merge sha f285b2d0 concluded success.</x:v>
+      </x:c>
       <x:c r="AC7" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5863,7 +5863,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/AGENTS.md</x:v>
       </x:c>
       <x:c r="Q21" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R21" s="39" t="str">
         <x:v>ctrl-vm-2256-06ac44fc</x:v>
@@ -5876,20 +5876,24 @@
         <x:v>2026-07-02T07:46:27Z</x:v>
       </x:c>
       <x:c r="V21" s="39" t="str">
-        <x:v>2026-07-02T07:46:39Z</x:v>
-      </x:c>
-      <x:c r="W21" s="39" t="str">
-        <x:v>2026-07-02T09:46:39Z</x:v>
-      </x:c>
-      <x:c r="X21" s="39"/>
+        <x:v>2026-07-02T17:57:32Z</x:v>
+      </x:c>
+      <x:c r="W21" s="39"/>
+      <x:c r="X21" s="39" t="str">
+        <x:v>2026-07-02T17:57:32Z</x:v>
+      </x:c>
       <x:c r="Y21" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z21" s="39" t="str">
-        <x:v>Implemented run-identity ambiguity + attempt binding in poll_pr_checks.py; PR #1261 open (fast-path CI green, 7 tests). Authority-file change awaits human review + native-green.</x:v>
-      </x:c>
-      <x:c r="AA21" s="39"/>
-      <x:c r="AB21" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA21" s="39" t="str">
+        <x:v>Delivered via merged PR #1261 (commit 5554809): poll_pr_checks.py now blocks ambiguous run identity (&gt;1 distinct run for the head SHA) and binds/verifies the run attempt, extending #934's head-SHA/event/workflow-name identity and ambiguous-job guards. 7 new tests.</x:v>
+      </x:c>
+      <x:c r="AB21" s="39" t="str">
+        <x:v>python3 -m unittest tests.test_poll_pr_checks -&gt; 46 tests OK; fast-path CI (validate/linux-fast/export) green on PR #1261; merged to main.</x:v>
+      </x:c>
       <x:c r="AC21" s="39" t="n">
         <x:v>2</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4777,7 +4777,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/prompts/codex-workflow-optimizer.md</x:v>
       </x:c>
       <x:c r="Q9" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R9" s="39" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
@@ -4790,20 +4790,24 @@
         <x:v>2026-07-02T15:55:04Z</x:v>
       </x:c>
       <x:c r="V9" s="39" t="str">
-        <x:v>2026-07-02T15:55:04Z</x:v>
-      </x:c>
-      <x:c r="W9" s="39" t="str">
-        <x:v>2026-07-02T17:55:04Z</x:v>
-      </x:c>
-      <x:c r="X9" s="39"/>
+        <x:v>2026-07-03T04:08:32Z</x:v>
+      </x:c>
+      <x:c r="W9" s="39"/>
+      <x:c r="X9" s="39" t="str">
+        <x:v>2026-07-03T04:08:32Z</x:v>
+      </x:c>
       <x:c r="Y9" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z9" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
-      </x:c>
-      <x:c r="AA9" s="39"/>
-      <x:c r="AB9" s="39"/>
+        <x:v>Completed by controller ctrl-vm-4027-c0afa077 after squash-merge of PR #1313.</x:v>
+      </x:c>
+      <x:c r="AA9" s="39" t="str">
+        <x:v>Implemented by PR #1313 (squash-merged as 49a786ec): scripts/worker_report.py stdlib-only CLI (create/validate/render/handoff/registry-payload) with schema v1 worker reports (owner/claimId/issue/branch/filesChanged/commands with per-command outcomes and exit codes/ciHeadSha/outcome), identity and CI-SHA cross-validation, deterministic bounded restart handoffs (10-item section cap), optional subagent_registry bridge; doc sections in AGENTS.md, docs/codex-agent-queue.md, prompt pointers.</x:v>
+      </x:c>
+      <x:c r="AB9" s="39" t="str">
+        <x:v>tests.test_worker_report 16 OK; tests/ discovery 583 OK (1 _game skip); tests.test_prompt_inventory OK; validate_content OK; black -l 120 clean; indentation clean. Python tooling suites green in PR runs; merged to main as 49a786ec.</x:v>
+      </x:c>
       <x:c r="AC9" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4698,25 +4698,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/prompts/codex-queue-controller.md</x:v>
       </x:c>
       <x:c r="Q8" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R8" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R8" s="36" t="str">
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
+      </x:c>
       <x:c r="S8" s="36"/>
-      <x:c r="T8" s="36"/>
-      <x:c r="U8" s="36"/>
-      <x:c r="V8" s="36"/>
-      <x:c r="W8" s="36"/>
+      <x:c r="T8" s="36" t="str">
+        <x:v>e769e133-2cee-4540-ab52-fc289143e905</x:v>
+      </x:c>
+      <x:c r="U8" s="36" t="str">
+        <x:v>2026-07-03T05:04:22Z</x:v>
+      </x:c>
+      <x:c r="V8" s="36" t="str">
+        <x:v>2026-07-03T05:04:22Z</x:v>
+      </x:c>
+      <x:c r="W8" s="36" t="str">
+        <x:v>2026-07-03T07:04:22Z</x:v>
+      </x:c>
       <x:c r="X8" s="36"/>
       <x:c r="Y8" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z8" s="36" t="str">
-        <x:v>Migrated from GitHub issue #620; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
       </x:c>
       <x:c r="AA8" s="36"/>
       <x:c r="AB8" s="36"/>
       <x:c r="AC8" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4526,25 +4526,39 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/coverage_report.py</x:v>
       </x:c>
       <x:c r="Q6" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R6" s="36"/>
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="R6" s="36" t="str">
+        <x:v>ctrl-vm-2617-4ae45d4e</x:v>
+      </x:c>
       <x:c r="S6" s="36"/>
-      <x:c r="T6" s="36"/>
-      <x:c r="U6" s="36"/>
-      <x:c r="V6" s="36"/>
+      <x:c r="T6" s="36" t="str">
+        <x:v>4069f9fd-ce0e-4efe-8f17-93a636df7f22</x:v>
+      </x:c>
+      <x:c r="U6" s="36" t="str">
+        <x:v>2026-07-03T08:59:32Z</x:v>
+      </x:c>
+      <x:c r="V6" s="36" t="str">
+        <x:v>2026-07-03T08:59:32Z</x:v>
+      </x:c>
       <x:c r="W6" s="36"/>
-      <x:c r="X6" s="36"/>
+      <x:c r="X6" s="36" t="str">
+        <x:v>2026-07-03T08:59:32Z</x:v>
+      </x:c>
       <x:c r="Y6" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z6" s="36" t="str">
-        <x:v>Migrated from GitHub issue #618; not yet claimed.</x:v>
-      </x:c>
-      <x:c r="AA6" s="36"/>
-      <x:c r="AB6" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA6" s="36" t="str">
+        <x:v>Delivered via merged PR #1342: additive change-KIND taxonomy on ci_change_classifier.py + _path_kind, GitHub outputs, src/gui/** coverage-lock test. build.yml gating unchanged. Human-reviewed and merged (authority file).</x:v>
+      </x:c>
+      <x:c r="AB6" s="36" t="str">
+        <x:v>unittest ci_change_classifier+poll_pr_checks+prompt_inventory -&gt; 74 OK; merged to main.</x:v>
+      </x:c>
       <x:c r="AC6" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4167,25 +4167,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q2" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R2" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R2" s="36" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-46</x:v>
+      </x:c>
       <x:c r="S2" s="36"/>
-      <x:c r="T2" s="36"/>
-      <x:c r="U2" s="36"/>
-      <x:c r="V2" s="36"/>
-      <x:c r="W2" s="36"/>
+      <x:c r="T2" s="36" t="str">
+        <x:v>94e6906b-988f-4f1a-b318-5d060bd9991a</x:v>
+      </x:c>
+      <x:c r="U2" s="36" t="str">
+        <x:v>2026-07-03T09:10:41Z</x:v>
+      </x:c>
+      <x:c r="V2" s="36" t="str">
+        <x:v>2026-07-03T09:10:41Z</x:v>
+      </x:c>
+      <x:c r="W2" s="36" t="str">
+        <x:v>2026-07-03T12:10:41Z</x:v>
+      </x:c>
       <x:c r="X2" s="36"/>
       <x:c r="Y2" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z2" s="36" t="str">
-        <x:v>Migrated from GitHub issue #614; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-46</x:v>
       </x:c>
       <x:c r="AA2" s="36"/>
       <x:c r="AB2" s="36"/>
       <x:c r="AC2" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4712,7 +4712,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/prompts/codex-queue-controller.md</x:v>
       </x:c>
       <x:c r="Q8" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R8" s="36" t="str">
         <x:v>controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
@@ -4725,20 +4725,24 @@
         <x:v>2026-07-03T05:04:22Z</x:v>
       </x:c>
       <x:c r="V8" s="36" t="str">
-        <x:v>2026-07-03T05:04:22Z</x:v>
-      </x:c>
-      <x:c r="W8" s="36" t="str">
-        <x:v>2026-07-03T07:04:22Z</x:v>
-      </x:c>
-      <x:c r="X8" s="36"/>
+        <x:v>2026-07-03T11:22:28Z</x:v>
+      </x:c>
+      <x:c r="W8" s="36"/>
+      <x:c r="X8" s="36" t="str">
+        <x:v>2026-07-03T11:22:28Z</x:v>
+      </x:c>
       <x:c r="Y8" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z8" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4027-c0afa077/subagent-7</x:v>
-      </x:c>
-      <x:c r="AA8" s="36"/>
-      <x:c r="AB8" s="36"/>
+        <x:v>Completed by controller ctrl-vm-4027-c0afa077 after squash-merge of PR #1354 (green CI on updated branch onto green main).</x:v>
+      </x:c>
+      <x:c r="AA8" s="36" t="str">
+        <x:v>Implemented by PR #1354 (squash-merged as f3cf8ac2): scripts/controller_policy.py canonical stdlib-only policy module (SCHEMA_VERSION, PolicyField dataclass with value/type/bounds/enum/description + errors(), POLICY registry, value()/heartbeat_interval_minutes() accessors, canonical QUEUE_STATUSES/QUEUE_PRIORITIES/TARGET_FILE_OVERLAP_POLICIES, validate() with cross-field checks, schemaPayload(), fast-check CLI). scripts/issue_queue.py and scripts/subagent_registry.py derive their legacy constants/CLI defaults from the policy via guarded imports; no numeric value changed. Docs/prompt reference the canonical source.</x:v>
+      </x:c>
+      <x:c r="AB8" s="36" t="str">
+        <x:v>GREEN on PR #1354 CI run 28656339768 (conclusion success, all jobs). tests.test_controller_policy 11 OK; tests.test_issue_queue 46 OK; tests.test_subagent_registry 17 OK; tests.test_prompt_inventory 7 OK; tests.test_worker_report 16 OK; full tests/ discovery 702 OK; black -l 120 clean; 4-space indentation clean; validate_content OK.</x:v>
+      </x:c>
       <x:c r="AC8" s="36" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4899,25 +4899,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/docs/codex-agent-queue.md</x:v>
       </x:c>
       <x:c r="Q10" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R10" s="36"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R10" s="36" t="str">
+        <x:v>controller/ctrl-lis-2-14d26144/subagent-1</x:v>
+      </x:c>
       <x:c r="S10" s="36"/>
-      <x:c r="T10" s="36"/>
-      <x:c r="U10" s="36"/>
-      <x:c r="V10" s="36"/>
-      <x:c r="W10" s="36"/>
+      <x:c r="T10" s="36" t="str">
+        <x:v>d0707cc7-e3ad-4b04-a939-e9e616e61293</x:v>
+      </x:c>
+      <x:c r="U10" s="36" t="str">
+        <x:v>2026-07-06T03:09:28Z</x:v>
+      </x:c>
+      <x:c r="V10" s="36" t="str">
+        <x:v>2026-07-06T03:09:28Z</x:v>
+      </x:c>
+      <x:c r="W10" s="36" t="str">
+        <x:v>2026-07-07T03:09:28Z</x:v>
+      </x:c>
       <x:c r="X10" s="36"/>
       <x:c r="Y10" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z10" s="36" t="str">
-        <x:v>Migrated from GitHub issue #622; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-lis-2-14d26144/subagent-1</x:v>
       </x:c>
       <x:c r="AA10" s="36"/>
       <x:c r="AB10" s="36"/>
       <x:c r="AC10" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4167,25 +4167,39 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/issue_queue.py</x:v>
       </x:c>
       <x:c r="Q2" s="36" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R2" s="36"/>
+        <x:v>DONE</x:v>
+      </x:c>
+      <x:c r="R2" s="36" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-55</x:v>
+      </x:c>
       <x:c r="S2" s="36"/>
-      <x:c r="T2" s="36"/>
-      <x:c r="U2" s="36"/>
-      <x:c r="V2" s="36"/>
+      <x:c r="T2" s="36" t="str">
+        <x:v>68129181-22e8-4bd4-a4a2-b4b0dafa4e32</x:v>
+      </x:c>
+      <x:c r="U2" s="36" t="str">
+        <x:v>2026-07-08T10:48:53Z</x:v>
+      </x:c>
+      <x:c r="V2" s="36" t="str">
+        <x:v>2026-07-08T10:48:53Z</x:v>
+      </x:c>
       <x:c r="W2" s="36"/>
-      <x:c r="X2" s="36"/>
+      <x:c r="X2" s="36" t="str">
+        <x:v>2026-07-08T10:48:53Z</x:v>
+      </x:c>
       <x:c r="Y2" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z2" s="36" t="str">
-        <x:v>Migrated from GitHub issue #614; not yet claimed.</x:v>
-      </x:c>
-      <x:c r="AA2" s="36"/>
-      <x:c r="AB2" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA2" s="36" t="str">
+        <x:v>Reconciliation record: #614 is already delivered on main. scripts/controller_reconciler.py (snapshot/reconcile/next-action; read-only, deterministic, idempotency keys) landed via the foundation PR #1349 and was completed with the claim_pr_open/claim_pr_merged lifecycle states plus 28 tests in tests/test_controller_reconciler.py via PR #1364 (merged a5542550). This duplicate row in the migrated workbook is closed against those merged PRs; no new implementation was needed.</x:v>
+      </x:c>
+      <x:c r="AB2" s="36" t="str">
+        <x:v>Verified on current main: scripts/controller_reconciler.py and tests/test_controller_reconciler.py exist with claim_pr states present; delivering PRs #1349/#1364 merged; duplicate rows of this issue in other workbooks already DONE.</x:v>
+      </x:c>
       <x:c r="AC2" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5003,25 +5003,35 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/poll_pr_checks.py</x:v>
       </x:c>
       <x:c r="Q11" s="39" t="str">
-        <x:v>NOT_STARTED</x:v>
-      </x:c>
-      <x:c r="R11" s="39"/>
+        <x:v>IN_PROGRESS</x:v>
+      </x:c>
+      <x:c r="R11" s="39" t="str">
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-60</x:v>
+      </x:c>
       <x:c r="S11" s="39"/>
-      <x:c r="T11" s="39"/>
-      <x:c r="U11" s="39"/>
-      <x:c r="V11" s="39"/>
-      <x:c r="W11" s="39"/>
+      <x:c r="T11" s="39" t="str">
+        <x:v>3390230a-45c6-459f-b1fe-f12a2fb31bb2</x:v>
+      </x:c>
+      <x:c r="U11" s="39" t="str">
+        <x:v>2026-07-09T04:30:04Z</x:v>
+      </x:c>
+      <x:c r="V11" s="39" t="str">
+        <x:v>2026-07-09T04:30:04Z</x:v>
+      </x:c>
+      <x:c r="W11" s="39" t="str">
+        <x:v>2026-07-09T06:00:04Z</x:v>
+      </x:c>
       <x:c r="X11" s="39"/>
       <x:c r="Y11" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z11" s="39" t="str">
-        <x:v>Migrated from GitHub issue #623; not yet claimed.</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-60</x:v>
       </x:c>
       <x:c r="AA11" s="39"/>
       <x:c r="AB11" s="39"/>
       <x:c r="AC11" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -5003,7 +5003,7 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/scripts/poll_pr_checks.py</x:v>
       </x:c>
       <x:c r="Q11" s="39" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R11" s="39" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-60</x:v>
@@ -5016,20 +5016,24 @@
         <x:v>2026-07-09T04:30:04Z</x:v>
       </x:c>
       <x:c r="V11" s="39" t="str">
-        <x:v>2026-07-09T04:30:04Z</x:v>
-      </x:c>
-      <x:c r="W11" s="39" t="str">
-        <x:v>2026-07-09T06:00:04Z</x:v>
-      </x:c>
-      <x:c r="X11" s="39"/>
+        <x:v>2026-07-09T05:08:25Z</x:v>
+      </x:c>
+      <x:c r="W11" s="39"/>
+      <x:c r="X11" s="39" t="str">
+        <x:v>2026-07-09T05:08:25Z</x:v>
+      </x:c>
       <x:c r="Y11" s="39" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z11" s="39" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-60</x:v>
-      </x:c>
-      <x:c r="AA11" s="39"/>
-      <x:c r="AB11" s="39"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA11" s="39" t="str">
+        <x:v>Read-only PR preflight in pr_review_audit.py: deterministic verdict taxonomy (allow/allow_replacement/reject_duplicate_open/already_delivered/cannot_verify fail-closed), advisory-only scope/title warnings, JSON in/out with shell-gateable exit codes, issue_queue payload builder, controller docs. Both Codex findings fixed (object-shaped snapshots routed through loadRecords + doc example branches on nonzero exit). 240 tests green. Delivered by PR #1454 (merged).</x:v>
+      </x:c>
+      <x:c r="AB11" s="39" t="str">
+        <x:v>PR #1454 CI green on fix commit 6c17063a (all required lanes); squash-merged to main at efd8c03b.</x:v>
+      </x:c>
       <x:c r="AC11" s="39" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4916,32 +4916,32 @@
         <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R10" s="36" t="str">
-        <x:v>controller/ctrl-lis-2-14d26144/subagent-1</x:v>
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-63</x:v>
       </x:c>
       <x:c r="S10" s="36"/>
       <x:c r="T10" s="36" t="str">
-        <x:v>d0707cc7-e3ad-4b04-a939-e9e616e61293</x:v>
+        <x:v>0d2a37d1-1e85-4dde-aca2-7b95984e8786</x:v>
       </x:c>
       <x:c r="U10" s="36" t="str">
-        <x:v>2026-07-06T03:09:28Z</x:v>
+        <x:v>2026-07-13T04:33:43Z</x:v>
       </x:c>
       <x:c r="V10" s="36" t="str">
-        <x:v>2026-07-06T03:09:28Z</x:v>
+        <x:v>2026-07-13T04:33:43Z</x:v>
       </x:c>
       <x:c r="W10" s="36" t="str">
-        <x:v>2026-07-07T03:09:28Z</x:v>
+        <x:v>2026-07-13T06:03:43Z</x:v>
       </x:c>
       <x:c r="X10" s="36"/>
       <x:c r="Y10" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z10" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-lis-2-14d26144/subagent-1</x:v>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-63</x:v>
       </x:c>
       <x:c r="AA10" s="36"/>
       <x:c r="AB10" s="36"/>
       <x:c r="AC10" s="36" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">

--- a/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
+++ b/planning/fall_of_nouraajd_github_issues_implementation_workbook_migrated.xlsx
@@ -4913,35 +4913,39 @@
 https://raw.githubusercontent.com/lisu188/fall-of-nouraajd/main/docs/codex-agent-queue.md</x:v>
       </x:c>
       <x:c r="Q10" s="36" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R10" s="36" t="str">
-        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-63</x:v>
+        <x:v>controller/ctrl-vm-4027-c0afa077/subagent-27</x:v>
       </x:c>
       <x:c r="S10" s="36"/>
       <x:c r="T10" s="36" t="str">
-        <x:v>0d2a37d1-1e85-4dde-aca2-7b95984e8786</x:v>
+        <x:v>ff361dae-b4dc-4ead-9003-4a7816f2ddcf</x:v>
       </x:c>
       <x:c r="U10" s="36" t="str">
-        <x:v>2026-07-13T04:33:43Z</x:v>
+        <x:v>2026-07-19T08:51:56Z</x:v>
       </x:c>
       <x:c r="V10" s="36" t="str">
-        <x:v>2026-07-13T04:33:43Z</x:v>
-      </x:c>
-      <x:c r="W10" s="36" t="str">
-        <x:v>2026-07-13T06:03:43Z</x:v>
-      </x:c>
-      <x:c r="X10" s="36"/>
+        <x:v>2026-07-19T08:52:08Z</x:v>
+      </x:c>
+      <x:c r="W10" s="36"/>
+      <x:c r="X10" s="36" t="str">
+        <x:v>2026-07-19T08:52:08Z</x:v>
+      </x:c>
       <x:c r="Y10" s="36" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z10" s="36" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-63</x:v>
-      </x:c>
-      <x:c r="AA10" s="36"/>
-      <x:c r="AB10" s="36"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA10" s="36" t="str">
+        <x:v>Landed the reclaimed #622 implementation (PR #1462): scripts/heartbeat_scheduler.py adds a pure scheduler deriving not_due/due_soon/due/overdue/recovery_required states solely from issue_queue.claimTimingHealth() and one captured UTC timestamp, plus worker-poll evidence validation (identity/liveness/freshness), read-only planning + apply --dry-run, and atomic multi-claim publication under the workbook lock (prevalidate all, one shared timestamp, max(existing,now+lease) preservation, single atomicSave, byte restoration on failure). Existing single-claim heartbeat API/CLI unchanged. Additive tooling only (no build.yml/AGENTS.md changes).</x:v>
+      </x:c>
+      <x:c r="AB10" s="36" t="str">
+        <x:v>CI green on PR #1462 (rebased onto current main): validate/export/linux-fast/linux/windows-deps/windows all success (linux-coverage skipped, no src). tests/test_heartbeat_scheduler.py covers due/overdue boundaries, identity/liveness evidence, duplicate/mixed-validity all-or-nothing batches, lease preservation, single-save multi-row, byte preservation, CLI immutability. Squash-merged to main as 83e47380.</x:v>
+      </x:c>
       <x:c r="AC10" s="36" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
